--- a/YRIGOYEN 9115/Mayo/YRIGOYEN-EXPENSAS-MAYO.xlsx
+++ b/YRIGOYEN 9115/Mayo/YRIGOYEN-EXPENSAS-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9115\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A82078-ECED-42BD-9811-83D87FBD1AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEE96A4-B451-4EA9-8DB5-E1B1A1FF886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -528,15 +528,9 @@
     <t>QUIEN NO INFORME EL PAGO DE LA MANERA SOLICITADA CORRE EL RIESGO DE NO VER EL MISMO IMPUTADO. SE SOSTIENE EL MONTO DE EXPENSAS YA QUE SE PROCEDERA A LIMPIAR LOS TANQUES DE AGUA Y DESPUES DE LA ASAMBLEA SE DECIDIRA LA OBRA QUE SE REALIZARA EN LOS MISMOS.</t>
   </si>
   <si>
-    <t>JPL articulos de limpieza</t>
-  </si>
-  <si>
     <t xml:space="preserve"> le imputamos 223235 a el 7C cuando le correspondia al 10C</t>
   </si>
   <si>
-    <t>Casa Monini - Compra de articulos</t>
-  </si>
-  <si>
     <t>Sanitarios roma - arena y cemento</t>
   </si>
   <si>
@@ -553,9 +547,6 @@
   </si>
   <si>
     <t>Debito 14/04</t>
-  </si>
-  <si>
-    <t>Servisur -Mano de obra y materiales</t>
   </si>
   <si>
     <t>Doartero - Cambio de flotante de tanque de alta presion con boya</t>
@@ -599,6 +590,15 @@
   </si>
   <si>
     <t>Agustin plomero - Cuota 2 de 2 - Rotura baño y cocina distribuidor de agua caliente - Piso 9A</t>
+  </si>
+  <si>
+    <t>Vaciamiento de guardia con bomba propia y del consorciopor ganado de agua de napa - Se asiste hasta su vaciamiento el dia 16/05 con personal</t>
+  </si>
+  <si>
+    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable - Anticipo cuota 1 de 4</t>
+  </si>
+  <si>
+    <t>Casa Koruk</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1426,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1698,216 +1698,225 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="44" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2392,13 +2401,13 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="169" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
-      <c r="I3" s="170"/>
-      <c r="J3" s="171"/>
+      <c r="F3" s="172" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="174"/>
       <c r="K3" s="147"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -2413,11 +2422,11 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="145"/>
-      <c r="F4" s="172"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="174"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="177"/>
       <c r="K4" s="147"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -2426,20 +2435,20 @@
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15"/>
-      <c r="B5" s="178">
+      <c r="B5" s="181">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="178"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="16"/>
       <c r="E5" s="146">
         <v>0</v>
       </c>
-      <c r="F5" s="172"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="174"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="177"/>
       <c r="K5" s="148"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -2454,11 +2463,11 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="145"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="177"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="179"/>
+      <c r="H6" s="179"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="180"/>
       <c r="K6" s="148"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -2467,11 +2476,11 @@
     </row>
     <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
-      <c r="B7" s="178">
+      <c r="B7" s="181">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="178"/>
+      <c r="C7" s="181"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -3055,7 +3064,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E19" s="30">
         <v>2.4899999999999999E-2</v>
@@ -3759,7 +3768,7 @@
         <v>357270.25318546098</v>
       </c>
       <c r="P32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
@@ -3916,7 +3925,7 @@
         <v>388377.32772576308</v>
       </c>
       <c r="P35" s="168" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
@@ -4380,23 +4389,23 @@
     </row>
     <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="38"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="188"/>
+      <c r="D2" s="225"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="227"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="189" t="s">
+      <c r="E3" s="228" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="189"/>
-      <c r="G3" s="189"/>
-      <c r="H3" s="190"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="228"/>
+      <c r="H3" s="229"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="38"/>
@@ -4441,13 +4450,13 @@
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H8" s="81"/>
     </row>
@@ -4464,16 +4473,16 @@
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="191" t="s">
+      <c r="A10" s="230" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="192"/>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="192"/>
-      <c r="H10" s="193"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="231"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="232"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
@@ -4486,16 +4495,16 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="194" t="s">
+      <c r="A12" s="233" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="194"/>
-      <c r="C12" s="194"/>
-      <c r="D12" s="194"/>
-      <c r="E12" s="194"/>
-      <c r="F12" s="194"/>
-      <c r="G12" s="194"/>
-      <c r="H12" s="194"/>
+      <c r="B12" s="233"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="233"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="233"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="153" t="s">
@@ -4556,19 +4565,19 @@
       <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="195" t="s">
-        <v>184</v>
-      </c>
-      <c r="B17" s="195"/>
-      <c r="C17" s="195"/>
-      <c r="D17" s="195"/>
-      <c r="E17" s="195"/>
-      <c r="F17" s="195"/>
-      <c r="G17" s="195"/>
-      <c r="H17" s="195"/>
+      <c r="A17" s="234" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="234"/>
+      <c r="C17" s="234"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="234"/>
+      <c r="F17" s="234"/>
+      <c r="G17" s="234"/>
+      <c r="H17" s="234"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="239" t="s">
+      <c r="A18" s="170" t="s">
         <v>164</v>
       </c>
       <c r="B18" s="154"/>
@@ -4577,12 +4586,12 @@
       <c r="E18" s="154"/>
       <c r="F18" s="154"/>
       <c r="G18" s="154"/>
-      <c r="H18" s="238">
+      <c r="H18" s="169">
         <v>47000</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="239" t="s">
+      <c r="A19" s="170" t="s">
         <v>163</v>
       </c>
       <c r="B19" s="154"/>
@@ -4619,30 +4628,30 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="195" t="s">
+      <c r="A22" s="234" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="195"/>
-      <c r="C22" s="195"/>
-      <c r="D22" s="195"/>
-      <c r="E22" s="195"/>
-      <c r="F22" s="195"/>
-      <c r="G22" s="195"/>
-      <c r="H22" s="195"/>
+      <c r="B22" s="234"/>
+      <c r="C22" s="234"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="234"/>
+      <c r="G22" s="234"/>
+      <c r="H22" s="234"/>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="153" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="158" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C23" s="158"/>
       <c r="D23" s="158"/>
       <c r="E23" s="158"/>
       <c r="F23" s="158"/>
       <c r="G23" s="154"/>
-      <c r="H23" s="238">
+      <c r="H23" s="169">
         <v>89169.8</v>
       </c>
     </row>
@@ -4659,7 +4668,7 @@
       <c r="E24" s="158"/>
       <c r="F24" s="158"/>
       <c r="G24" s="154"/>
-      <c r="H24" s="238">
+      <c r="H24" s="169">
         <v>45117.56</v>
       </c>
     </row>
@@ -4676,7 +4685,7 @@
       <c r="E25" s="158"/>
       <c r="F25" s="158"/>
       <c r="G25" s="154"/>
-      <c r="H25" s="238">
+      <c r="H25" s="169">
         <v>5013.0600000000004</v>
       </c>
     </row>
@@ -4685,18 +4694,18 @@
         <v>161</v>
       </c>
       <c r="B26" s="154" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158"/>
       <c r="E26" s="158"/>
       <c r="F26" s="158"/>
       <c r="G26" s="154"/>
-      <c r="H26" s="240">
+      <c r="H26" s="171">
         <v>776011.89</v>
       </c>
       <c r="I26" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -4727,16 +4736,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="185" t="s">
+      <c r="A29" s="224" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="185"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
+      <c r="B29" s="224"/>
+      <c r="C29" s="224"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="224"/>
+      <c r="H29" s="224"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="154" t="s">
@@ -4748,7 +4757,7 @@
       <c r="E30" s="154"/>
       <c r="F30" s="154"/>
       <c r="G30" s="154"/>
-      <c r="H30" s="238">
+      <c r="H30" s="169">
         <v>3959.29</v>
       </c>
     </row>
@@ -4764,11 +4773,11 @@
       <c r="E31" s="154"/>
       <c r="F31" s="154"/>
       <c r="G31" s="154"/>
-      <c r="H31" s="238">
+      <c r="H31" s="169">
         <v>344838.6</v>
       </c>
       <c r="I31" s="168" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -4783,7 +4792,7 @@
       <c r="E32" s="154"/>
       <c r="F32" s="154"/>
       <c r="G32" s="154"/>
-      <c r="H32" s="238">
+      <c r="H32" s="169">
         <v>186828.01</v>
       </c>
     </row>
@@ -4803,16 +4812,16 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="185" t="s">
+      <c r="A34" s="224" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="185"/>
-      <c r="C34" s="185"/>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="185"/>
-      <c r="G34" s="185"/>
-      <c r="H34" s="185"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="85"/>
@@ -4834,7 +4843,7 @@
       <c r="E36" s="154"/>
       <c r="F36" s="154"/>
       <c r="G36" s="154"/>
-      <c r="H36" s="238">
+      <c r="H36" s="169">
         <v>140000</v>
       </c>
     </row>
@@ -4848,14 +4857,14 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="238">
+      <c r="H37" s="169">
         <v>38000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="85" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B38" s="162"/>
       <c r="C38" s="85"/>
@@ -4870,7 +4879,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="85" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B39" s="162"/>
       <c r="C39" s="85"/>
@@ -4878,14 +4887,14 @@
       <c r="E39" s="85"/>
       <c r="F39" s="85"/>
       <c r="G39" s="85"/>
-      <c r="H39" s="238">
+      <c r="H39" s="169">
         <v>18500</v>
       </c>
       <c r="J39" s="87"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="85" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B40" s="161"/>
       <c r="C40" s="154"/>
@@ -4893,13 +4902,13 @@
       <c r="E40" s="154"/>
       <c r="F40" s="154"/>
       <c r="G40" s="154"/>
-      <c r="H40" s="238">
+      <c r="H40" s="169">
         <v>58000</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="85" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B41" s="161"/>
       <c r="C41" s="154"/>
@@ -4910,11 +4919,11 @@
       <c r="H41" s="82">
         <v>300000</v>
       </c>
-      <c r="J41" s="202"/>
+      <c r="J41" s="185"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="85" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B42" s="161"/>
       <c r="C42" s="154"/>
@@ -4925,11 +4934,11 @@
       <c r="H42" s="82">
         <v>44800.12</v>
       </c>
-      <c r="J42" s="202"/>
+      <c r="J42" s="185"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="85" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B43" s="161"/>
       <c r="C43" s="154"/>
@@ -4941,41 +4950,41 @@
         <v>121997.24</v>
       </c>
       <c r="I43" s="149"/>
-      <c r="J43" s="202"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="B44" s="161"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="154"/>
-      <c r="E44" s="154"/>
-      <c r="F44" s="154"/>
-      <c r="G44" s="154"/>
-      <c r="H44" s="82">
-        <v>15379.52</v>
-      </c>
-      <c r="J44" s="202"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="85" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" s="161"/>
-      <c r="C45" s="154"/>
-      <c r="D45" s="154"/>
-      <c r="E45" s="154"/>
-      <c r="F45" s="154"/>
-      <c r="G45" s="154"/>
-      <c r="H45" s="82">
-        <v>65000</v>
-      </c>
-      <c r="J45" s="202"/>
+      <c r="J43" s="185"/>
+    </row>
+    <row r="44" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="241" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="242"/>
+      <c r="C44" s="242"/>
+      <c r="D44" s="242"/>
+      <c r="E44" s="242"/>
+      <c r="F44" s="242"/>
+      <c r="G44" s="243"/>
+      <c r="H44" s="169">
+        <v>450000</v>
+      </c>
+      <c r="J44" s="185"/>
+    </row>
+    <row r="45" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="182" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" s="183"/>
+      <c r="C45" s="183"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
+      <c r="F45" s="183"/>
+      <c r="G45" s="184"/>
+      <c r="H45" s="169">
+        <v>741000</v>
+      </c>
+      <c r="J45" s="185"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="85" t="s">
-        <v>166</v>
+      <c r="A46" s="170" t="s">
+        <v>189</v>
       </c>
       <c r="B46" s="161"/>
       <c r="C46" s="154"/>
@@ -4983,14 +4992,14 @@
       <c r="E46" s="154"/>
       <c r="F46" s="154"/>
       <c r="G46" s="154"/>
-      <c r="H46" s="82">
-        <v>146300</v>
-      </c>
-      <c r="J46" s="202"/>
+      <c r="H46" s="169">
+        <v>20000</v>
+      </c>
+      <c r="J46" s="185"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="85" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B47" s="161"/>
       <c r="C47" s="154"/>
@@ -4998,7 +5007,7 @@
       <c r="E47" s="154"/>
       <c r="F47" s="154"/>
       <c r="G47" s="154"/>
-      <c r="H47" s="238">
+      <c r="H47" s="169">
         <v>450000</v>
       </c>
     </row>
@@ -5014,20 +5023,20 @@
       <c r="G48" s="154"/>
       <c r="H48" s="84">
         <f>SUM(H35:H47)</f>
-        <v>1512976.88</v>
+        <v>2497297.36</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="185" t="s">
+      <c r="A49" s="224" t="s">
         <v>115</v>
       </c>
-      <c r="B49" s="185"/>
-      <c r="C49" s="185"/>
-      <c r="D49" s="185"/>
-      <c r="E49" s="185"/>
-      <c r="F49" s="185"/>
-      <c r="G49" s="185"/>
-      <c r="H49" s="185"/>
+      <c r="B49" s="224"/>
+      <c r="C49" s="224"/>
+      <c r="D49" s="224"/>
+      <c r="E49" s="224"/>
+      <c r="F49" s="224"/>
+      <c r="G49" s="224"/>
+      <c r="H49" s="224"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="154" t="s">
@@ -5035,17 +5044,17 @@
       </c>
       <c r="B50" s="154"/>
       <c r="C50" s="154" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D50" s="163"/>
       <c r="E50" s="154"/>
       <c r="F50" s="154"/>
       <c r="G50" s="154"/>
-      <c r="H50" s="238">
+      <c r="H50" s="169">
         <v>250000</v>
       </c>
       <c r="J50" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5053,12 +5062,12 @@
         <v>149</v>
       </c>
       <c r="B51" s="154"/>
-      <c r="C51" s="181"/>
-      <c r="D51" s="182"/>
+      <c r="C51" s="220"/>
+      <c r="D51" s="221"/>
       <c r="E51" s="165"/>
       <c r="F51" s="158"/>
       <c r="G51" s="154"/>
-      <c r="H51" s="238">
+      <c r="H51" s="169">
         <v>28000</v>
       </c>
     </row>
@@ -5088,16 +5097,16 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="196" t="s">
+      <c r="A54" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="197"/>
-      <c r="C54" s="197"/>
-      <c r="D54" s="197"/>
-      <c r="E54" s="197"/>
-      <c r="F54" s="197"/>
-      <c r="G54" s="197"/>
-      <c r="H54" s="198"/>
+      <c r="B54" s="236"/>
+      <c r="C54" s="236"/>
+      <c r="D54" s="236"/>
+      <c r="E54" s="236"/>
+      <c r="F54" s="236"/>
+      <c r="G54" s="236"/>
+      <c r="H54" s="237"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="154" t="s">
@@ -5139,16 +5148,16 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="196" t="s">
+      <c r="A58" s="235" t="s">
         <v>119</v>
       </c>
-      <c r="B58" s="197"/>
-      <c r="C58" s="197"/>
-      <c r="D58" s="197"/>
-      <c r="E58" s="197"/>
-      <c r="F58" s="197"/>
-      <c r="G58" s="197"/>
-      <c r="H58" s="198"/>
+      <c r="B58" s="236"/>
+      <c r="C58" s="236"/>
+      <c r="D58" s="236"/>
+      <c r="E58" s="236"/>
+      <c r="F58" s="236"/>
+      <c r="G58" s="236"/>
+      <c r="H58" s="237"/>
       <c r="I58" s="87"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
@@ -5199,16 +5208,16 @@
       <c r="K61" s="83"/>
     </row>
     <row r="62" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="199" t="s">
+      <c r="A62" s="238" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="200"/>
-      <c r="C62" s="200"/>
-      <c r="D62" s="200"/>
-      <c r="E62" s="200"/>
-      <c r="F62" s="200"/>
-      <c r="G62" s="200"/>
-      <c r="H62" s="201"/>
+      <c r="B62" s="239"/>
+      <c r="C62" s="239"/>
+      <c r="D62" s="239"/>
+      <c r="E62" s="239"/>
+      <c r="F62" s="239"/>
+      <c r="G62" s="239"/>
+      <c r="H62" s="240"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="86"/>
@@ -5263,15 +5272,15 @@
       <c r="H67" s="92"/>
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="183" t="s">
+      <c r="A68" s="222" t="s">
         <v>155</v>
       </c>
-      <c r="B68" s="184"/>
-      <c r="C68" s="184"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
-      <c r="F68" s="184"/>
-      <c r="G68" s="184"/>
+      <c r="B68" s="223"/>
+      <c r="C68" s="223"/>
+      <c r="D68" s="223"/>
+      <c r="E68" s="223"/>
+      <c r="F68" s="223"/>
+      <c r="G68" s="223"/>
       <c r="H68" s="128"/>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5320,25 +5329,25 @@
       <c r="H72" s="92"/>
     </row>
     <row r="73" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A73" s="231" t="s">
+      <c r="A73" s="216" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="231"/>
-      <c r="C73" s="231"/>
-      <c r="D73" s="231"/>
-      <c r="E73" s="231"/>
-      <c r="F73" s="231"/>
-      <c r="G73" s="231"/>
+      <c r="B73" s="216"/>
+      <c r="C73" s="216"/>
+      <c r="D73" s="216"/>
+      <c r="E73" s="216"/>
+      <c r="F73" s="216"/>
+      <c r="G73" s="216"/>
       <c r="H73" s="95"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="232"/>
-      <c r="B74" s="233"/>
-      <c r="C74" s="233"/>
-      <c r="D74" s="233"/>
-      <c r="E74" s="233"/>
-      <c r="F74" s="233"/>
-      <c r="G74" s="234"/>
+      <c r="A74" s="182"/>
+      <c r="B74" s="183"/>
+      <c r="C74" s="183"/>
+      <c r="D74" s="183"/>
+      <c r="E74" s="183"/>
+      <c r="F74" s="183"/>
+      <c r="G74" s="184"/>
       <c r="H74" s="124"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -5352,13 +5361,13 @@
       <c r="H75" s="124"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="235"/>
-      <c r="B76" s="236"/>
-      <c r="C76" s="236"/>
-      <c r="D76" s="236"/>
-      <c r="E76" s="236"/>
-      <c r="F76" s="236"/>
-      <c r="G76" s="237"/>
+      <c r="A76" s="217"/>
+      <c r="B76" s="218"/>
+      <c r="C76" s="218"/>
+      <c r="D76" s="218"/>
+      <c r="E76" s="218"/>
+      <c r="F76" s="218"/>
+      <c r="G76" s="219"/>
       <c r="H76" s="82">
         <v>0</v>
       </c>
@@ -5414,15 +5423,15 @@
       <c r="I80" s="87"/>
     </row>
     <row r="81" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="179" t="s">
+      <c r="A81" s="198" t="s">
         <v>122</v>
       </c>
-      <c r="B81" s="180"/>
-      <c r="C81" s="180"/>
-      <c r="D81" s="180"/>
-      <c r="E81" s="180"/>
-      <c r="F81" s="180"/>
-      <c r="G81" s="180"/>
+      <c r="B81" s="199"/>
+      <c r="C81" s="199"/>
+      <c r="D81" s="199"/>
+      <c r="E81" s="199"/>
+      <c r="F81" s="199"/>
+      <c r="G81" s="199"/>
       <c r="H81" s="140">
         <f>H79</f>
         <v>0</v>
@@ -5430,75 +5439,75 @@
       <c r="I81" s="87"/>
     </row>
     <row r="82" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="228" t="s">
+      <c r="A82" s="213" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="229"/>
-      <c r="C82" s="229"/>
-      <c r="D82" s="229"/>
-      <c r="E82" s="229"/>
-      <c r="F82" s="229"/>
-      <c r="G82" s="230"/>
+      <c r="B82" s="214"/>
+      <c r="C82" s="214"/>
+      <c r="D82" s="214"/>
+      <c r="E82" s="214"/>
+      <c r="F82" s="214"/>
+      <c r="G82" s="215"/>
       <c r="H82" s="140"/>
       <c r="I82" s="88"/>
     </row>
     <row r="83" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="212" t="s">
+      <c r="A83" s="195" t="s">
         <v>143</v>
       </c>
-      <c r="B83" s="213"/>
-      <c r="C83" s="213"/>
-      <c r="D83" s="213"/>
-      <c r="E83" s="213"/>
-      <c r="F83" s="213"/>
-      <c r="G83" s="214"/>
+      <c r="B83" s="196"/>
+      <c r="C83" s="196"/>
+      <c r="D83" s="196"/>
+      <c r="E83" s="196"/>
+      <c r="F83" s="196"/>
+      <c r="G83" s="197"/>
       <c r="H83" s="140"/>
       <c r="I83" s="87"/>
       <c r="J83" s="83"/>
     </row>
     <row r="84" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A84" s="179" t="s">
+      <c r="A84" s="198" t="s">
         <v>124</v>
       </c>
-      <c r="B84" s="180"/>
-      <c r="C84" s="180"/>
-      <c r="D84" s="180"/>
-      <c r="E84" s="180"/>
-      <c r="F84" s="180"/>
-      <c r="G84" s="180"/>
+      <c r="B84" s="199"/>
+      <c r="C84" s="199"/>
+      <c r="D84" s="199"/>
+      <c r="E84" s="199"/>
+      <c r="F84" s="199"/>
+      <c r="G84" s="199"/>
       <c r="H84" s="140">
         <f>H65+H61+H57+H53+H48+H33+H16+H21+H28+H71</f>
-        <v>4188521.65</v>
+        <v>5172842.1300000008</v>
       </c>
       <c r="I84" s="83"/>
     </row>
     <row r="85" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A85" s="215" t="s">
+      <c r="A85" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="B85" s="216"/>
-      <c r="C85" s="216"/>
-      <c r="D85" s="216"/>
-      <c r="E85" s="216"/>
-      <c r="F85" s="216"/>
-      <c r="G85" s="217"/>
+      <c r="B85" s="201"/>
+      <c r="C85" s="201"/>
+      <c r="D85" s="201"/>
+      <c r="E85" s="201"/>
+      <c r="F85" s="201"/>
+      <c r="G85" s="202"/>
       <c r="H85" s="141">
         <f>H84+H82</f>
-        <v>4188521.65</v>
+        <v>5172842.1300000008</v>
       </c>
       <c r="I85" s="83"/>
       <c r="K85" s="149"/>
     </row>
     <row r="86" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A86" s="215" t="s">
+      <c r="A86" s="200" t="s">
         <v>126</v>
       </c>
-      <c r="B86" s="216"/>
-      <c r="C86" s="216"/>
-      <c r="D86" s="216"/>
-      <c r="E86" s="216"/>
-      <c r="F86" s="216"/>
-      <c r="G86" s="217"/>
+      <c r="B86" s="201"/>
+      <c r="C86" s="201"/>
+      <c r="D86" s="201"/>
+      <c r="E86" s="201"/>
+      <c r="F86" s="201"/>
+      <c r="G86" s="202"/>
       <c r="H86" s="142">
         <f>H81+H83</f>
         <v>0</v>
@@ -5506,30 +5515,30 @@
       <c r="I86" s="83"/>
     </row>
     <row r="87" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="218" t="s">
+      <c r="A87" s="203" t="s">
         <v>127</v>
       </c>
-      <c r="B87" s="219"/>
-      <c r="C87" s="219"/>
-      <c r="D87" s="219"/>
-      <c r="E87" s="219"/>
-      <c r="F87" s="219"/>
-      <c r="G87" s="219"/>
+      <c r="B87" s="204"/>
+      <c r="C87" s="204"/>
+      <c r="D87" s="204"/>
+      <c r="E87" s="204"/>
+      <c r="F87" s="204"/>
+      <c r="G87" s="204"/>
       <c r="H87" s="143">
         <f>H84+H81</f>
-        <v>4188521.65</v>
+        <v>5172842.1300000008</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="220" t="s">
+      <c r="A88" s="205" t="s">
         <v>128</v>
       </c>
-      <c r="B88" s="221"/>
-      <c r="C88" s="221"/>
-      <c r="D88" s="221"/>
-      <c r="E88" s="221"/>
-      <c r="F88" s="221"/>
-      <c r="G88" s="221"/>
+      <c r="B88" s="206"/>
+      <c r="C88" s="206"/>
+      <c r="D88" s="206"/>
+      <c r="E88" s="206"/>
+      <c r="F88" s="206"/>
+      <c r="G88" s="206"/>
       <c r="H88" s="100">
         <v>0</v>
       </c>
@@ -5545,26 +5554,26 @@
       <c r="H89" s="102"/>
     </row>
     <row r="90" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="222" t="s">
+      <c r="A90" s="207" t="s">
         <v>165</v>
       </c>
-      <c r="B90" s="223"/>
-      <c r="C90" s="223"/>
-      <c r="D90" s="223"/>
-      <c r="E90" s="223"/>
-      <c r="F90" s="223"/>
-      <c r="G90" s="223"/>
-      <c r="H90" s="224"/>
+      <c r="B90" s="208"/>
+      <c r="C90" s="208"/>
+      <c r="D90" s="208"/>
+      <c r="E90" s="208"/>
+      <c r="F90" s="208"/>
+      <c r="G90" s="208"/>
+      <c r="H90" s="209"/>
     </row>
     <row r="91" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="225"/>
-      <c r="B91" s="226"/>
-      <c r="C91" s="226"/>
-      <c r="D91" s="226"/>
-      <c r="E91" s="226"/>
-      <c r="F91" s="226"/>
-      <c r="G91" s="226"/>
-      <c r="H91" s="227"/>
+      <c r="A91" s="210"/>
+      <c r="B91" s="211"/>
+      <c r="C91" s="211"/>
+      <c r="D91" s="211"/>
+      <c r="E91" s="211"/>
+      <c r="F91" s="211"/>
+      <c r="G91" s="211"/>
+      <c r="H91" s="212"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
@@ -5577,16 +5586,16 @@
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A93" s="203" t="s">
+      <c r="A93" s="186" t="s">
         <v>129</v>
       </c>
-      <c r="B93" s="204"/>
-      <c r="C93" s="204"/>
-      <c r="D93" s="204"/>
-      <c r="E93" s="204"/>
-      <c r="F93" s="204"/>
-      <c r="G93" s="204"/>
-      <c r="H93" s="205"/>
+      <c r="B93" s="187"/>
+      <c r="C93" s="187"/>
+      <c r="D93" s="187"/>
+      <c r="E93" s="187"/>
+      <c r="F93" s="187"/>
+      <c r="G93" s="187"/>
+      <c r="H93" s="188"/>
     </row>
     <row r="94" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A94" s="103" t="s">
@@ -5629,7 +5638,7 @@
       <c r="G96" s="108"/>
       <c r="H96" s="123">
         <f>-H87</f>
-        <v>-4188521.65</v>
+        <v>-5172842.1300000008</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -5649,7 +5658,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="107" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B98" s="108"/>
       <c r="C98" s="108"/>
@@ -5663,7 +5672,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="107" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B99" s="108"/>
       <c r="C99" s="108"/>
@@ -5702,21 +5711,21 @@
       <c r="G101" s="111"/>
       <c r="H101" s="112">
         <f>SUM(H94:H100)</f>
-        <v>2126224.9556154204</v>
+        <v>1141904.4756154194</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="103" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="206" t="s">
+      <c r="A103" s="189" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="207"/>
-      <c r="C103" s="207"/>
-      <c r="D103" s="207"/>
-      <c r="E103" s="207"/>
-      <c r="F103" s="207"/>
-      <c r="G103" s="207"/>
-      <c r="H103" s="208"/>
+      <c r="B103" s="190"/>
+      <c r="C103" s="190"/>
+      <c r="D103" s="190"/>
+      <c r="E103" s="190"/>
+      <c r="F103" s="190"/>
+      <c r="G103" s="190"/>
+      <c r="H103" s="191"/>
     </row>
     <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="113" t="s">
@@ -5844,58 +5853,67 @@
         <v>101</v>
       </c>
       <c r="B120" s="120"/>
-      <c r="C120" s="209">
+      <c r="C120" s="192">
         <f>SUM(D116:D119)</f>
         <v>0</v>
       </c>
-      <c r="D120" s="210"/>
+      <c r="D120" s="193"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="211"/>
-      <c r="B123" s="211"/>
-      <c r="C123" s="211"/>
-      <c r="D123" s="211"/>
-      <c r="E123" s="211"/>
-      <c r="F123" s="211"/>
-      <c r="G123" s="211"/>
-      <c r="H123" s="211"/>
+      <c r="A123" s="194"/>
+      <c r="B123" s="194"/>
+      <c r="C123" s="194"/>
+      <c r="D123" s="194"/>
+      <c r="E123" s="194"/>
+      <c r="F123" s="194"/>
+      <c r="G123" s="194"/>
+      <c r="H123" s="194"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="211"/>
-      <c r="B124" s="211"/>
-      <c r="C124" s="211"/>
-      <c r="D124" s="211"/>
-      <c r="E124" s="211"/>
-      <c r="F124" s="211"/>
-      <c r="G124" s="211"/>
-      <c r="H124" s="211"/>
+      <c r="A124" s="194"/>
+      <c r="B124" s="194"/>
+      <c r="C124" s="194"/>
+      <c r="D124" s="194"/>
+      <c r="E124" s="194"/>
+      <c r="F124" s="194"/>
+      <c r="G124" s="194"/>
+      <c r="H124" s="194"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="211"/>
-      <c r="B125" s="211"/>
-      <c r="C125" s="211"/>
-      <c r="D125" s="211"/>
-      <c r="E125" s="211"/>
-      <c r="F125" s="211"/>
-      <c r="G125" s="211"/>
-      <c r="H125" s="211"/>
+      <c r="A125" s="194"/>
+      <c r="B125" s="194"/>
+      <c r="C125" s="194"/>
+      <c r="D125" s="194"/>
+      <c r="E125" s="194"/>
+      <c r="F125" s="194"/>
+      <c r="G125" s="194"/>
+      <c r="H125" s="194"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="211"/>
-      <c r="B126" s="211"/>
-      <c r="C126" s="211"/>
-      <c r="D126" s="211"/>
-      <c r="E126" s="211"/>
-      <c r="F126" s="211"/>
-      <c r="G126" s="211"/>
-      <c r="H126" s="211"/>
+      <c r="A126" s="194"/>
+      <c r="B126" s="194"/>
+      <c r="C126" s="194"/>
+      <c r="D126" s="194"/>
+      <c r="E126" s="194"/>
+      <c r="F126" s="194"/>
+      <c r="G126" s="194"/>
+      <c r="H126" s="194"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="J41:J46"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="C120:D120"/>
+  <mergeCells count="33">
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A123:H126"/>
     <mergeCell ref="A83:G83"/>
     <mergeCell ref="A84:G84"/>
@@ -5904,6 +5922,11 @@
     <mergeCell ref="A87:G87"/>
     <mergeCell ref="A88:G88"/>
     <mergeCell ref="A90:H91"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="J41:J46"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="C120:D120"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="A73:G73"/>
     <mergeCell ref="A74:G74"/>
@@ -5911,18 +5934,6 @@
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A62:H62"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/YRIGOYEN 9115/Mayo/YRIGOYEN-EXPENSAS-MAYO.xlsx
+++ b/YRIGOYEN 9115/Mayo/YRIGOYEN-EXPENSAS-MAYO.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9115\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEE96A4-B451-4EA9-8DB5-E1B1A1FF886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9184C9A-439A-4117-9232-04C393FDA2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$122</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$119</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="183">
   <si>
     <t xml:space="preserve">Banco Comafi:
 Cons. Prop. Edif. Yrigoyen 9115 CUIT: 30-56975974-5
@@ -267,9 +267,6 @@
     <t>Favio Felice</t>
   </si>
   <si>
-    <t>Macarena</t>
-  </si>
-  <si>
     <t>9° D</t>
   </si>
   <si>
@@ -489,9 +486,6 @@
     <t>Marcelina Valvuena</t>
   </si>
   <si>
-    <t>Daniel Salguero</t>
-  </si>
-  <si>
     <t xml:space="preserve">FATHERY </t>
   </si>
   <si>
@@ -504,9 +498,6 @@
     <t>Gastos part</t>
   </si>
   <si>
-    <t>Fumigacion Lanus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Merlina </t>
   </si>
   <si>
@@ -528,31 +519,7 @@
     <t>QUIEN NO INFORME EL PAGO DE LA MANERA SOLICITADA CORRE EL RIESGO DE NO VER EL MISMO IMPUTADO. SE SOSTIENE EL MONTO DE EXPENSAS YA QUE SE PROCEDERA A LIMPIAR LOS TANQUES DE AGUA Y DESPUES DE LA ASAMBLEA SE DECIDIRA LA OBRA QUE SE REALIZARA EN LOS MISMOS.</t>
   </si>
   <si>
-    <t xml:space="preserve"> le imputamos 223235 a el 7C cuando le correspondia al 10C</t>
-  </si>
-  <si>
-    <t>Sanitarios roma - arena y cemento</t>
-  </si>
-  <si>
-    <t>Sanitarios roma - Articulos varios</t>
-  </si>
-  <si>
     <t>AUMENTADOS EN abri 2025</t>
-  </si>
-  <si>
-    <t>Trabajo de albañileria - Piccutelli Juan Jose - Trabajo 4B</t>
-  </si>
-  <si>
-    <t>Debito 09/04</t>
-  </si>
-  <si>
-    <t>Debito 14/04</t>
-  </si>
-  <si>
-    <t>Doartero - Cambio de flotante de tanque de alta presion con boya</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados 10c</t>
   </si>
   <si>
     <t>Ingreso mal contabilizado al 7C - Ya imputado al 10C</t>
@@ -562,9 +529,6 @@
 </t>
   </si>
   <si>
-    <t>HABIA PAGADO LO QUE LE CORRESPONDIA EL MES PASADO</t>
-  </si>
-  <si>
     <t>VTO: 16/06</t>
   </si>
   <si>
@@ -580,25 +544,40 @@
     <t>Destapacion Italoamericana - Mantenimiento de cañerias, repaso de camaras de cloacas, salida colectora AYSA</t>
   </si>
   <si>
-    <t>en el foleo hay dos arcas, y este (de 776011,89) es mucho mas alto del mes pasado</t>
-  </si>
-  <si>
     <t>Salvatierra Matias - Desobstruccion columna cocina 8B</t>
   </si>
   <si>
-    <t>este aysa es muy menor al del mes anterior</t>
-  </si>
-  <si>
     <t>Agustin plomero - Cuota 2 de 2 - Rotura baño y cocina distribuidor de agua caliente - Piso 9A</t>
   </si>
   <si>
-    <t>Vaciamiento de guardia con bomba propia y del consorciopor ganado de agua de napa - Se asiste hasta su vaciamiento el dia 16/05 con personal</t>
-  </si>
-  <si>
     <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable - Anticipo cuota 1 de 4</t>
   </si>
   <si>
-    <t>Casa Koruk</t>
+    <t>Debito 07/05</t>
+  </si>
+  <si>
+    <t>Debito 12/05</t>
+  </si>
+  <si>
+    <t>Fumigacion Lanus 13/05</t>
+  </si>
+  <si>
+    <t>Sanitarios roma - compra caños de gas para perdida del dpto 9</t>
+  </si>
+  <si>
+    <t>Vaciamiento de guardia con bomba propia y del consorciopor ganado de agua de napa - Se asiste hasta su vaciamiento el dia 16/05 con personal - imputado a la uf PA</t>
+  </si>
+  <si>
+    <t>Casa Koruk - compra de botas para la encargada</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados 8C</t>
+  </si>
+  <si>
+    <t>Daniel Salgueiro</t>
+  </si>
+  <si>
+    <t>Macarena perez ruiz</t>
   </si>
 </sst>
 </file>
@@ -606,14 +585,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -1423,10 +1402,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1446,7 +1425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1455,11 +1434,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1472,7 +1451,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1484,7 +1463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1492,15 +1471,15 @@
     <xf numFmtId="10" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1531,7 +1510,7 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1541,17 +1520,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1567,28 +1546,28 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="26" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1599,48 +1578,48 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1653,31 +1632,31 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1685,7 +1664,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1696,40 +1675,74 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1740,35 +1753,32 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1779,12 +1789,6 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1824,39 +1828,6 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1887,7 +1858,7 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2334,26 +2305,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="70" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="70" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="70" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="70" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="70" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="70" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="70" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="70" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="70" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="70" customWidth="1"/>
     <col min="11" max="11" width="9" style="70" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2376,7 +2347,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -2393,7 +2364,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12">
@@ -2401,20 +2372,20 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="172" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="174"/>
+      <c r="F3" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="169"/>
       <c r="K3" s="147"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -2422,40 +2393,40 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="145"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="176"/>
-      <c r="I4" s="176"/>
-      <c r="J4" s="177"/>
+      <c r="F4" s="170"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="172"/>
       <c r="K4" s="147"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="181">
+      <c r="B5" s="176">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="181"/>
+      <c r="C5" s="176"/>
       <c r="D5" s="16"/>
       <c r="E5" s="146">
         <v>0</v>
       </c>
-      <c r="F5" s="175"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="177"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="172"/>
       <c r="K5" s="148"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15"/>
       <c r="B6" s="17" t="s">
         <v>2</v>
@@ -2463,24 +2434,24 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="145"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="179"/>
-      <c r="H6" s="179"/>
-      <c r="I6" s="179"/>
-      <c r="J6" s="180"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="174"/>
+      <c r="J6" s="175"/>
       <c r="K6" s="148"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="181">
+      <c r="B7" s="176">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="181"/>
+      <c r="C7" s="176"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2494,7 +2465,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>3</v>
       </c>
@@ -2526,7 +2497,7 @@
         <v>12</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L8" s="20" t="s">
         <v>13</v>
@@ -2541,7 +2512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>1</v>
       </c>
@@ -2556,10 +2527,11 @@
         <v>0.108</v>
       </c>
       <c r="F9" s="31">
-        <v>563591.05020000006</v>
+        <v>534000.05020000006</v>
       </c>
       <c r="G9" s="150">
-        <v>569591</v>
+        <f>F9</f>
+        <v>534000.05020000006</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H42" si="0">IF(F9&gt;G9,F9-G9,0)</f>
@@ -2571,7 +2543,7 @@
       </c>
       <c r="J9" s="32">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
-        <v>5999.9497999999439</v>
+        <v>0</v>
       </c>
       <c r="K9" s="32"/>
       <c r="L9" s="33">
@@ -2584,14 +2556,14 @@
       </c>
       <c r="N9" s="34">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>534000.05020000006</v>
+        <v>540000</v>
       </c>
       <c r="O9" s="35">
         <f>N9*2% + N9</f>
-        <v>544680.05120400002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>550800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2</v>
       </c>
@@ -2606,11 +2578,11 @@
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="F10" s="31">
-        <v>150290.94672000001</v>
+        <v>144000</v>
       </c>
       <c r="G10" s="151">
         <f>F10</f>
-        <v>150290.94672000001</v>
+        <v>144000</v>
       </c>
       <c r="H10" s="32">
         <f t="shared" si="0"/>
@@ -2642,7 +2614,7 @@
         <v>146880</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>3</v>
       </c>
@@ -2657,10 +2629,10 @@
         <v>2.5600000000000001E-2</v>
       </c>
       <c r="F11" s="31">
-        <v>136263.54967758546</v>
+        <v>127999.54967758546</v>
       </c>
       <c r="G11" s="151">
-        <v>136264</v>
+        <v>130560</v>
       </c>
       <c r="H11" s="32">
         <f t="shared" si="0"/>
@@ -2672,7 +2644,7 @@
       </c>
       <c r="J11" s="32">
         <f t="shared" si="2"/>
-        <v>0.45032241454464383</v>
+        <v>2560.4503224145446</v>
       </c>
       <c r="K11" s="32"/>
       <c r="L11" s="33">
@@ -2685,14 +2657,14 @@
       </c>
       <c r="N11" s="34">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>127999.54967758546</v>
+        <v>125439.54967758546</v>
       </c>
       <c r="O11" s="35">
         <f t="shared" si="6"/>
-        <v>130559.54067113716</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>127948.34067113716</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>4</v>
       </c>
@@ -2707,11 +2679,11 @@
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F12" s="31">
-        <v>112196.366475</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="G12" s="151">
         <f>F12</f>
-        <v>112196.366475</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="H12" s="32">
         <f t="shared" si="0"/>
@@ -2744,7 +2716,7 @@
       </c>
       <c r="P12" s="38"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <v>5</v>
       </c>
@@ -2755,17 +2727,17 @@
         <v>26</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E13" s="30">
         <v>1.7299999999999999E-2</v>
       </c>
       <c r="F13" s="31">
-        <v>90278.936744999999</v>
+        <v>86500</v>
       </c>
       <c r="G13" s="151">
         <f>F13</f>
-        <v>90278.936744999999</v>
+        <v>86500</v>
       </c>
       <c r="H13" s="32">
         <f t="shared" si="0"/>
@@ -2797,7 +2769,7 @@
         <v>88230</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>6</v>
       </c>
@@ -2812,10 +2784,10 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F14" s="31">
-        <v>147866.92475261347</v>
+        <v>139366.92475261347</v>
       </c>
       <c r="G14" s="151">
-        <v>148000</v>
+        <v>140000</v>
       </c>
       <c r="H14" s="32">
         <f t="shared" si="0"/>
@@ -2827,7 +2799,7 @@
       </c>
       <c r="J14" s="32">
         <f t="shared" si="2"/>
-        <v>133.07524738652864</v>
+        <v>633.07524738652864</v>
       </c>
       <c r="K14" s="32"/>
       <c r="L14" s="33">
@@ -2840,14 +2812,14 @@
       </c>
       <c r="N14" s="34">
         <f t="shared" si="5"/>
-        <v>139366.92475261347</v>
+        <v>138866.92475261347</v>
       </c>
       <c r="O14" s="35">
         <f t="shared" si="6"/>
-        <v>142154.26324766575</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141644.26324766575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>7</v>
       </c>
@@ -2862,11 +2834,11 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F15" s="31">
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="G15" s="151">
         <f>F15</f>
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="H15" s="32">
         <f t="shared" si="0"/>
@@ -2898,7 +2870,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>8</v>
       </c>
@@ -2909,16 +2881,17 @@
         <v>32</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E16" s="30">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F16" s="31">
-        <v>112196.366475</v>
+        <v>105256.07647499999</v>
       </c>
       <c r="G16" s="151">
-        <v>114440.29</v>
+        <f>F16</f>
+        <v>105256.07647499999</v>
       </c>
       <c r="H16" s="32">
         <f t="shared" si="0"/>
@@ -2930,7 +2903,7 @@
       </c>
       <c r="J16" s="32">
         <f t="shared" si="2"/>
-        <v>2243.9235249999911</v>
+        <v>0</v>
       </c>
       <c r="K16" s="32"/>
       <c r="L16" s="33">
@@ -2943,14 +2916,14 @@
       </c>
       <c r="N16" s="34">
         <f t="shared" si="5"/>
-        <v>105256.07647499999</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="O16" s="35">
         <f t="shared" si="6"/>
-        <v>107361.19800449999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>109649.99999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>9</v>
       </c>
@@ -2961,22 +2934,22 @@
         <v>34</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E17" s="30">
         <v>1.3599999999999999E-2</v>
       </c>
       <c r="F17" s="31">
-        <v>141697.87139130224</v>
+        <v>213948.80753304131</v>
       </c>
       <c r="G17" s="151"/>
       <c r="H17" s="32">
         <f t="shared" si="0"/>
-        <v>141697.87139130224</v>
+        <v>213948.80753304131</v>
       </c>
       <c r="I17" s="32">
         <f t="shared" si="1"/>
-        <v>4250.9361417390674</v>
+        <v>6418.4642259912389</v>
       </c>
       <c r="J17" s="32">
         <f t="shared" si="2"/>
@@ -2993,14 +2966,14 @@
       </c>
       <c r="N17" s="34">
         <f t="shared" si="5"/>
-        <v>213948.80753304131</v>
+        <v>288367.27175903256</v>
       </c>
       <c r="O17" s="35">
         <f t="shared" si="6"/>
-        <v>218227.78368370215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>294134.61719421321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>10</v>
       </c>
@@ -3008,20 +2981,20 @@
         <v>35</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E18" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F18" s="31">
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="G18" s="151">
         <f t="shared" ref="G18:G23" si="7">F18</f>
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="H18" s="32">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
@@ -3053,7 +3026,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <v>11</v>
       </c>
@@ -3064,17 +3037,17 @@
         <v>37</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E19" s="30">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F19" s="31">
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="G19" s="151">
         <f t="shared" si="7"/>
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="H19" s="32">
         <f t="shared" si="0"/>
@@ -3106,7 +3079,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>12</v>
       </c>
@@ -3121,20 +3094,23 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F20" s="31">
-        <v>191516.58835500001</v>
-      </c>
-      <c r="G20" s="151"/>
+        <v>380762.08600565005</v>
+      </c>
+      <c r="G20" s="151">
+        <f>400000</f>
+        <v>400000</v>
+      </c>
       <c r="H20" s="32">
         <f t="shared" si="0"/>
-        <v>191516.58835500001</v>
+        <v>0</v>
       </c>
       <c r="I20" s="32">
         <f t="shared" si="1"/>
-        <v>5745.4976506500007</v>
+        <v>0</v>
       </c>
       <c r="J20" s="32">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19237.913994349947</v>
       </c>
       <c r="K20" s="32"/>
       <c r="L20" s="33">
@@ -3147,14 +3123,14 @@
       </c>
       <c r="N20" s="34">
         <f t="shared" si="5"/>
-        <v>380762.08600565005</v>
+        <v>164262.08600565008</v>
       </c>
       <c r="O20" s="35">
         <f t="shared" si="6"/>
-        <v>388377.32772576308</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>167547.32772576308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>13</v>
       </c>
@@ -3165,17 +3141,16 @@
         <v>41</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E21" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F21" s="31">
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="G21" s="151">
-        <f t="shared" si="7"/>
-        <v>145594.354635</v>
+        <v>142290</v>
       </c>
       <c r="H21" s="32">
         <f t="shared" si="0"/>
@@ -3187,7 +3162,7 @@
       </c>
       <c r="J21" s="32">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2790</v>
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="33">
@@ -3200,14 +3175,14 @@
       </c>
       <c r="N21" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>136710</v>
       </c>
       <c r="O21" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>139444.20000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>14</v>
       </c>
@@ -3222,11 +3197,11 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F22" s="31">
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="G22" s="151">
         <f t="shared" si="7"/>
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="H22" s="32">
         <f t="shared" si="0"/>
@@ -3258,7 +3233,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <v>15</v>
       </c>
@@ -3269,17 +3244,17 @@
         <v>45</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E23" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F23" s="31">
-        <v>191516.58835500001</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="G23" s="151">
         <f t="shared" si="7"/>
-        <v>191516.58835500001</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="H23" s="32">
         <f t="shared" si="0"/>
@@ -3311,7 +3286,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>16</v>
       </c>
@@ -3322,24 +3297,24 @@
         <v>47</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E24" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F24" s="31">
-        <v>203930.46377982196</v>
+        <v>228323.19719321662</v>
       </c>
       <c r="G24" s="151">
-        <v>117694.35</v>
+        <v>139500</v>
       </c>
       <c r="H24" s="32">
         <f t="shared" si="0"/>
-        <v>86236.113779821957</v>
+        <v>88823.19719321662</v>
       </c>
       <c r="I24" s="32">
         <f t="shared" si="1"/>
-        <v>2587.0834133946587</v>
+        <v>2664.6959157964984</v>
       </c>
       <c r="J24" s="32">
         <f t="shared" si="2"/>
@@ -3356,14 +3331,14 @@
       </c>
       <c r="N24" s="34">
         <f t="shared" si="5"/>
-        <v>228323.19719321662</v>
+        <v>230987.89310901312</v>
       </c>
       <c r="O24" s="35">
         <f t="shared" si="6"/>
-        <v>232889.66113708096</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>235607.65097119339</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36">
         <v>17</v>
       </c>
@@ -3378,10 +3353,10 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F25" s="31">
-        <v>127456.775127</v>
+        <v>121956.77512699999</v>
       </c>
       <c r="G25" s="151">
-        <v>130000</v>
+        <v>124396</v>
       </c>
       <c r="H25" s="32">
         <f t="shared" si="0"/>
@@ -3393,7 +3368,7 @@
       </c>
       <c r="J25" s="32">
         <f t="shared" si="2"/>
-        <v>2543.2248729999992</v>
+        <v>2439.2248730000138</v>
       </c>
       <c r="K25" s="32"/>
       <c r="L25" s="33">
@@ -3406,14 +3381,14 @@
       </c>
       <c r="N25" s="34">
         <f t="shared" si="5"/>
-        <v>121956.77512699999</v>
+        <v>122060.77512699997</v>
       </c>
       <c r="O25" s="35">
         <f t="shared" si="6"/>
-        <v>124395.91062953998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124501.99062953997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>18</v>
       </c>
@@ -3428,10 +3403,10 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F26" s="31">
-        <v>191516.58835500001</v>
+        <v>183016.58835500004</v>
       </c>
       <c r="G26" s="151">
-        <v>192000</v>
+        <v>187000</v>
       </c>
       <c r="H26" s="32">
         <f t="shared" si="0"/>
@@ -3443,7 +3418,7 @@
       </c>
       <c r="J26" s="32">
         <f t="shared" si="2"/>
-        <v>483.41164499998558</v>
+        <v>3983.4116449999565</v>
       </c>
       <c r="K26" s="32"/>
       <c r="L26" s="33">
@@ -3456,14 +3431,14 @@
       </c>
       <c r="N26" s="34">
         <f t="shared" si="5"/>
-        <v>183016.58835500004</v>
+        <v>179516.58835500007</v>
       </c>
       <c r="O26" s="35">
         <f t="shared" si="6"/>
-        <v>186676.92012210004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>183106.92012210007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <v>19</v>
       </c>
@@ -3478,11 +3453,11 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F27" s="31">
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="G27" s="151">
         <f>F27</f>
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="H27" s="32">
         <f t="shared" si="0"/>
@@ -3514,7 +3489,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>20</v>
       </c>
@@ -3529,20 +3504,22 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F28" s="31">
-        <v>129938.46357255647</v>
-      </c>
-      <c r="G28" s="151"/>
+        <v>258336.61747973313</v>
+      </c>
+      <c r="G28" s="151">
+        <v>263503</v>
+      </c>
       <c r="H28" s="54">
         <f t="shared" si="0"/>
-        <v>129938.46357255647</v>
+        <v>0</v>
       </c>
       <c r="I28" s="32">
         <f t="shared" si="1"/>
-        <v>3898.1539071766942</v>
+        <v>0</v>
       </c>
       <c r="J28" s="32">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5166.3825202668668</v>
       </c>
       <c r="K28" s="32"/>
       <c r="L28" s="33">
@@ -3555,14 +3532,14 @@
       </c>
       <c r="N28" s="34">
         <f t="shared" si="5"/>
-        <v>258336.61747973313</v>
+        <v>119333.61747973312</v>
       </c>
       <c r="O28" s="35">
         <f t="shared" si="6"/>
-        <v>263503.34982932778</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>121720.28982932778</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <v>21</v>
       </c>
@@ -3573,17 +3550,16 @@
         <v>57</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E29" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F29" s="31">
-        <v>191516.58835500001</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="G29" s="151">
-        <f>F29</f>
-        <v>191516.58835500001</v>
+        <v>188000</v>
       </c>
       <c r="H29" s="32">
         <f t="shared" si="0"/>
@@ -3595,7 +3571,7 @@
       </c>
       <c r="J29" s="32">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4499.9999999999709</v>
       </c>
       <c r="K29" s="32"/>
       <c r="L29" s="33">
@@ -3608,14 +3584,14 @@
       </c>
       <c r="N29" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>179000.00000000006</v>
       </c>
       <c r="O29" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>182580.00000000006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>22</v>
       </c>
@@ -3632,11 +3608,11 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F30" s="31">
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="G30" s="151">
         <f>F30</f>
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="H30" s="32">
         <f t="shared" si="0"/>
@@ -3668,7 +3644,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>23</v>
       </c>
@@ -3683,16 +3659,16 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F31" s="31">
-        <v>129939.02868041999</v>
+        <v>258337.19954083255</v>
       </c>
       <c r="G31" s="151"/>
       <c r="H31" s="32">
         <f t="shared" si="0"/>
-        <v>129939.02868041999</v>
+        <v>258337.19954083255</v>
       </c>
       <c r="I31" s="32">
         <f t="shared" si="1"/>
-        <v>3898.1708604125993</v>
+        <v>7750.115986224976</v>
       </c>
       <c r="J31" s="32">
         <f t="shared" si="2"/>
@@ -3709,14 +3685,14 @@
       </c>
       <c r="N31" s="34">
         <f t="shared" si="5"/>
-        <v>258337.19954083255</v>
+        <v>390587.31552705751</v>
       </c>
       <c r="O31" s="35">
         <f t="shared" si="6"/>
-        <v>263503.94353164919</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>398399.06183759868</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
         <v>24</v>
       </c>
@@ -3727,24 +3703,25 @@
         <v>64</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F32" s="18">
-        <v>316907.72243047878</v>
+        <v>509914.95410339313</v>
       </c>
       <c r="G32" s="151">
-        <v>155000</v>
+        <f>43566+183500</f>
+        <v>227066</v>
       </c>
       <c r="H32" s="32">
         <f t="shared" si="0"/>
-        <v>161907.72243047878</v>
+        <v>282848.95410339313</v>
       </c>
       <c r="I32" s="32">
         <f t="shared" si="1"/>
-        <v>4857.2316729143631</v>
+        <v>8485.4686231017931</v>
       </c>
       <c r="J32" s="32">
         <f t="shared" si="2"/>
@@ -3761,17 +3738,14 @@
       </c>
       <c r="N32" s="34">
         <f t="shared" si="5"/>
-        <v>350264.95410339313</v>
+        <v>474834.42272649496</v>
       </c>
       <c r="O32" s="35">
         <f t="shared" si="6"/>
-        <v>357270.25318546098</v>
-      </c>
-      <c r="P32" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>484331.11118102487</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <f>A32+1</f>
         <v>25</v>
@@ -3789,20 +3763,22 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F33" s="122">
-        <v>287973.82392552152</v>
-      </c>
-      <c r="G33" s="151"/>
+        <v>436113.03864328715</v>
+      </c>
+      <c r="G33" s="151">
+        <v>444835.3</v>
+      </c>
       <c r="H33" s="32">
         <f t="shared" si="0"/>
-        <v>287973.82392552152</v>
+        <v>0</v>
       </c>
       <c r="I33" s="32">
         <f t="shared" si="1"/>
-        <v>8639.2147177656443</v>
+        <v>0</v>
       </c>
       <c r="J33" s="32">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8722.2613567128428</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="33">
@@ -3815,14 +3791,14 @@
       </c>
       <c r="N33" s="34">
         <f t="shared" si="5"/>
-        <v>436113.03864328715</v>
+        <v>130777.73864328716</v>
       </c>
       <c r="O33" s="35">
         <f t="shared" si="6"/>
-        <v>444835.29941615288</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133393.29341615291</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <f t="shared" ref="A34:A42" si="8">A33+1</f>
         <v>26</v>
@@ -3840,11 +3816,11 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F34" s="18">
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="G34" s="122">
         <f>F34</f>
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="H34" s="32">
         <f t="shared" si="0"/>
@@ -3876,7 +3852,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -3892,16 +3868,19 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F35" s="18">
-        <v>191516.58835500001</v>
-      </c>
-      <c r="G35" s="167"/>
+        <v>380762.08600565005</v>
+      </c>
+      <c r="G35" s="151">
+        <f>197262+183500</f>
+        <v>380762</v>
+      </c>
       <c r="H35" s="32">
         <f t="shared" si="0"/>
-        <v>191516.58835500001</v>
+        <v>8.6005650053266436E-2</v>
       </c>
       <c r="I35" s="32">
         <f t="shared" si="1"/>
-        <v>5745.4976506500007</v>
+        <v>2.580169501597993E-3</v>
       </c>
       <c r="J35" s="32">
         <f t="shared" si="2"/>
@@ -3918,17 +3897,15 @@
       </c>
       <c r="N35" s="34">
         <f t="shared" si="5"/>
-        <v>380762.08600565005</v>
+        <v>183500.08858581958</v>
       </c>
       <c r="O35" s="35">
         <f t="shared" si="6"/>
-        <v>388377.32772576308</v>
-      </c>
-      <c r="P35" s="168" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>187170.09035753598</v>
+      </c>
+      <c r="P35" s="87"/>
+    </row>
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -3946,11 +3923,11 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F36" s="18">
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="G36" s="122">
         <f>F36</f>
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="H36" s="32">
         <f t="shared" si="0"/>
@@ -3982,7 +3959,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -3994,17 +3971,17 @@
         <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E37" s="30">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F37" s="18">
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="G37" s="122">
         <f>F37</f>
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="H37" s="32">
         <f t="shared" si="0"/>
@@ -4036,7 +4013,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -4048,22 +4025,24 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="E38" s="30">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F38" s="18">
-        <v>223558.98744151148</v>
-      </c>
-      <c r="G38" s="151"/>
+        <v>337765.75706475682</v>
+      </c>
+      <c r="G38" s="151">
+        <v>107500</v>
+      </c>
       <c r="H38" s="32">
         <f t="shared" si="0"/>
-        <v>223558.98744151148</v>
+        <v>230265.75706475682</v>
       </c>
       <c r="I38" s="32">
         <f t="shared" si="1"/>
-        <v>6706.7696232453436</v>
+        <v>6907.9727119427043</v>
       </c>
       <c r="J38" s="32">
         <f t="shared" si="2"/>
@@ -4080,36 +4059,36 @@
       </c>
       <c r="N38" s="34">
         <f t="shared" si="5"/>
-        <v>337765.75706475682</v>
+        <v>344673.7297766995</v>
       </c>
       <c r="O38" s="35">
         <f t="shared" si="6"/>
-        <v>344521.07220605196</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>351567.20437223348</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="B39" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="56" t="s">
+      <c r="D39" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="E39" s="30">
         <v>1.3599999999999999E-2</v>
       </c>
       <c r="F39" s="18">
-        <v>70970.72484000001</v>
+        <v>68000</v>
       </c>
       <c r="G39" s="122">
         <f>F39</f>
-        <v>70970.72484000001</v>
+        <v>68000</v>
       </c>
       <c r="H39" s="32">
         <f t="shared" si="0"/>
@@ -4141,27 +4120,27 @@
         <v>69360</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="B40" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="56" t="s">
         <v>83</v>
-      </c>
-      <c r="C40" s="56" t="s">
-        <v>84</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F40" s="18">
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="G40" s="122">
         <f>F40</f>
-        <v>145594.354635</v>
+        <v>139500</v>
       </c>
       <c r="H40" s="32">
         <f t="shared" si="0"/>
@@ -4193,29 +4172,29 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="B41" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="56" t="s">
-        <v>86</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E41" s="30">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F41" s="18">
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="G41" s="122">
         <f>F41</f>
-        <v>129939.047685</v>
+        <v>124499.99999999999</v>
       </c>
       <c r="H41" s="32">
         <f t="shared" si="0"/>
@@ -4247,37 +4226,37 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="57">
         <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C42" s="59" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F42" s="60">
-        <v>572683.50820612558</v>
+        <v>296934.42345230939</v>
       </c>
       <c r="G42" s="152">
-        <f>223235+228216+11102</f>
-        <v>462553</v>
+        <f>155000+185500-43566</f>
+        <v>296934</v>
       </c>
       <c r="H42" s="32">
         <f t="shared" si="0"/>
-        <v>110130.50820612558</v>
+        <v>0.42345230939099565</v>
       </c>
       <c r="I42" s="32">
         <f t="shared" si="1"/>
-        <v>3303.9152461837675</v>
+        <v>1.2703569281729868E-2</v>
       </c>
       <c r="J42" s="32">
         <f t="shared" si="2"/>
@@ -4294,14 +4273,14 @@
       </c>
       <c r="N42" s="34">
         <f t="shared" si="5"/>
-        <v>296934.42345230939</v>
+        <v>183500.43615587871</v>
       </c>
       <c r="O42" s="35">
         <f t="shared" si="6"/>
-        <v>302873.11192135559</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>187170.44487899629</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
       <c r="B43" s="62"/>
       <c r="C43" s="63"/>
@@ -4312,23 +4291,23 @@
       </c>
       <c r="F43" s="65">
         <f>SUM(F9:F42)</f>
-        <v>6128524.8661349397</v>
+        <v>6869794.1316090701</v>
       </c>
       <c r="G43" s="144">
         <f t="shared" ref="G43:N43" si="9">SUM(G9:G42)</f>
-        <v>4485513.2054100009</v>
+        <v>5845602.4266750002</v>
       </c>
       <c r="H43" s="66">
         <f t="shared" si="9"/>
-        <v>1654415.6961377377</v>
+        <v>1074224.4248931999</v>
       </c>
       <c r="I43" s="67">
         <f t="shared" si="9"/>
-        <v>49632.470884132141</v>
+        <v>32226.732746795995</v>
       </c>
       <c r="J43" s="68">
         <f t="shared" si="9"/>
-        <v>11404.035412800993</v>
+        <v>50032.719959130671</v>
       </c>
       <c r="K43" s="130">
         <f t="shared" si="9"/>
@@ -4344,7 +4323,7 @@
       </c>
       <c r="N43" s="65">
         <f t="shared" si="9"/>
-        <v>6710144.1316090701</v>
+        <v>6073918.4376808656</v>
       </c>
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
@@ -4363,21 +4342,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K126"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4387,82 +4366,82 @@
       <c r="G1" s="72"/>
       <c r="H1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="227"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D2" s="219"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="221"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="222" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="228" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="229"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="223"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="D4" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="75" t="s">
-        <v>92</v>
-      </c>
       <c r="H4" s="76"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="D5" s="74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" s="77">
         <v>27231256879</v>
       </c>
       <c r="H5" s="76"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="D6" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" t="s">
         <v>94</v>
       </c>
-      <c r="G6" t="s">
-        <v>95</v>
-      </c>
       <c r="H6" s="76"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="D7" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="76"/>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="78" t="s">
         <v>96</v>
-      </c>
-      <c r="H7" s="76"/>
-    </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="78" t="s">
-        <v>97</v>
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H8" s="81"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -4472,19 +4451,19 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="230" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="231"/>
-      <c r="C10" s="231"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
-      <c r="F10" s="231"/>
-      <c r="G10" s="231"/>
-      <c r="H10" s="232"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="224" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="225"/>
+      <c r="C10" s="225"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="225"/>
+      <c r="H10" s="226"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4494,21 +4473,21 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="233" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="227" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="227"/>
+      <c r="C12" s="227"/>
+      <c r="D12" s="227"/>
+      <c r="E12" s="227"/>
+      <c r="F12" s="227"/>
+      <c r="G12" s="227"/>
+      <c r="H12" s="227"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="153" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="154"/>
       <c r="C13" s="154"/>
@@ -4517,12 +4496,12 @@
       <c r="F13" s="154"/>
       <c r="G13" s="154"/>
       <c r="H13" s="82">
-        <v>1002612.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1078821.3899999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="153" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B14" s="154"/>
       <c r="C14" s="154"/>
@@ -4531,12 +4510,12 @@
       <c r="F14" s="154"/>
       <c r="G14" s="154"/>
       <c r="H14" s="82">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="155" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B15" s="155"/>
       <c r="C15" s="155"/>
@@ -4545,12 +4524,12 @@
       <c r="F15" s="155"/>
       <c r="G15" s="155"/>
       <c r="H15" s="82">
-        <v>-218068.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>-234643.64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="156" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="157"/>
       <c r="C16" s="157"/>
@@ -4560,25 +4539,25 @@
       <c r="G16" s="157"/>
       <c r="H16" s="84">
         <f>SUM(H13:H15)</f>
-        <v>784545</v>
+        <v>844177.99999999988</v>
       </c>
       <c r="I16" s="83"/>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="234" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="234"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="170" t="s">
-        <v>164</v>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="228" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="228"/>
+      <c r="C17" s="228"/>
+      <c r="D17" s="228"/>
+      <c r="E17" s="228"/>
+      <c r="F17" s="228"/>
+      <c r="G17" s="228"/>
+      <c r="H17" s="228"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="85" t="s">
+        <v>161</v>
       </c>
       <c r="B18" s="154"/>
       <c r="C18" s="154"/>
@@ -4586,13 +4565,13 @@
       <c r="E18" s="154"/>
       <c r="F18" s="154"/>
       <c r="G18" s="154"/>
-      <c r="H18" s="169">
+      <c r="H18" s="82">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="170" t="s">
-        <v>163</v>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="85" t="s">
+        <v>160</v>
       </c>
       <c r="B19" s="154"/>
       <c r="C19" s="154"/>
@@ -4600,9 +4579,11 @@
       <c r="E19" s="154"/>
       <c r="F19" s="154"/>
       <c r="G19" s="154"/>
-      <c r="H19" s="82"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="82">
+        <v>3567.21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="154"/>
       <c r="B20" s="154"/>
       <c r="C20" s="154"/>
@@ -4612,9 +4593,9 @@
       <c r="G20" s="154"/>
       <c r="H20" s="82"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="154" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B21" s="154"/>
       <c r="C21" s="154"/>
@@ -4624,91 +4605,88 @@
       <c r="G21" s="154"/>
       <c r="H21" s="82">
         <f>SUM(H18:H20)</f>
-        <v>47000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="234" t="s">
+        <v>50567.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="228" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="228"/>
+      <c r="C22" s="228"/>
+      <c r="D22" s="228"/>
+      <c r="E22" s="228"/>
+      <c r="F22" s="228"/>
+      <c r="G22" s="228"/>
+      <c r="H22" s="228"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="153" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="234"/>
-      <c r="C22" s="234"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="234"/>
-      <c r="G22" s="234"/>
-      <c r="H22" s="234"/>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="153" t="s">
-        <v>105</v>
-      </c>
       <c r="B23" s="158" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C23" s="158"/>
       <c r="D23" s="158"/>
       <c r="E23" s="158"/>
       <c r="F23" s="158"/>
       <c r="G23" s="154"/>
-      <c r="H23" s="169">
+      <c r="H23" s="82">
         <v>89169.8</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="153" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B24" s="154" t="str">
         <f>B23</f>
-        <v>Debito 14/04</v>
+        <v>Debito 12/05</v>
       </c>
       <c r="C24" s="158"/>
       <c r="D24" s="158"/>
       <c r="E24" s="158"/>
       <c r="F24" s="158"/>
       <c r="G24" s="154"/>
-      <c r="H24" s="169">
+      <c r="H24" s="82">
         <v>45117.56</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="153" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="154" t="str">
         <f>B24</f>
-        <v>Debito 14/04</v>
+        <v>Debito 12/05</v>
       </c>
       <c r="C25" s="158"/>
       <c r="D25" s="158"/>
       <c r="E25" s="158"/>
       <c r="F25" s="158"/>
       <c r="G25" s="154"/>
-      <c r="H25" s="169">
+      <c r="H25" s="82">
         <v>5013.0600000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="153" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B26" s="154" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158"/>
       <c r="E26" s="158"/>
       <c r="F26" s="158"/>
       <c r="G26" s="154"/>
-      <c r="H26" s="171">
-        <v>776011.89</v>
-      </c>
-      <c r="I26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="82">
+        <v>461182.38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="153"/>
       <c r="B27" s="154"/>
       <c r="C27" s="158"/>
@@ -4720,9 +4698,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="157" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28" s="157"/>
       <c r="C28" s="157"/>
@@ -4732,24 +4710,24 @@
       <c r="G28" s="157"/>
       <c r="H28" s="84">
         <f>SUM(H23:H27)</f>
-        <v>915312.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="224" t="s">
+        <v>600482.80000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="218" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="218"/>
+      <c r="C29" s="218"/>
+      <c r="D29" s="218"/>
+      <c r="E29" s="218"/>
+      <c r="F29" s="218"/>
+      <c r="G29" s="218"/>
+      <c r="H29" s="218"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="154" t="s">
         <v>108</v>
-      </c>
-      <c r="B29" s="224"/>
-      <c r="C29" s="224"/>
-      <c r="D29" s="224"/>
-      <c r="E29" s="224"/>
-      <c r="F29" s="224"/>
-      <c r="G29" s="224"/>
-      <c r="H29" s="224"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="154" t="s">
-        <v>109</v>
       </c>
       <c r="B30" s="154"/>
       <c r="C30" s="154"/>
@@ -4757,48 +4735,46 @@
       <c r="E30" s="154"/>
       <c r="F30" s="154"/>
       <c r="G30" s="154"/>
-      <c r="H30" s="169">
+      <c r="H30" s="82">
         <v>3959.29</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="154" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="154" t="s">
         <v>110</v>
-      </c>
-      <c r="B31" s="154" t="s">
-        <v>111</v>
       </c>
       <c r="C31" s="154"/>
       <c r="D31" s="154"/>
       <c r="E31" s="154"/>
       <c r="F31" s="154"/>
       <c r="G31" s="154"/>
-      <c r="H31" s="169">
-        <v>344838.6</v>
-      </c>
-      <c r="I31" s="168" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="82">
+        <v>1229017.1299999999</v>
+      </c>
+      <c r="I31" s="87"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="159" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="154" t="s">
         <v>112</v>
-      </c>
-      <c r="B32" s="154" t="s">
-        <v>113</v>
       </c>
       <c r="C32" s="154"/>
       <c r="D32" s="154"/>
       <c r="E32" s="154"/>
       <c r="F32" s="154"/>
       <c r="G32" s="154"/>
-      <c r="H32" s="169">
+      <c r="H32" s="82">
         <v>186828.01</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="157" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="157"/>
       <c r="C33" s="157"/>
@@ -4808,22 +4784,22 @@
       <c r="G33" s="157"/>
       <c r="H33" s="160">
         <f>SUM(H30:H32)</f>
-        <v>535625.89999999991</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="224" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="224"/>
-      <c r="C34" s="224"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="224"/>
-      <c r="F34" s="224"/>
-      <c r="G34" s="224"/>
-      <c r="H34" s="224"/>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1419804.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="218" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="218"/>
+      <c r="C34" s="218"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="218"/>
+      <c r="H34" s="218"/>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
       <c r="B35" s="161"/>
       <c r="C35" s="154"/>
@@ -4833,9 +4809,9 @@
       <c r="G35" s="154"/>
       <c r="H35" s="82"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="85" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B36" s="161"/>
       <c r="C36" s="154"/>
@@ -4843,13 +4819,13 @@
       <c r="E36" s="154"/>
       <c r="F36" s="154"/>
       <c r="G36" s="154"/>
-      <c r="H36" s="169">
+      <c r="H36" s="82">
         <v>140000</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="85" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B37" s="162"/>
       <c r="C37" s="85"/>
@@ -4857,14 +4833,14 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="169">
+      <c r="H37" s="82">
         <v>38000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="85" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B38" s="162"/>
       <c r="C38" s="85"/>
@@ -4873,28 +4849,27 @@
       <c r="F38" s="85"/>
       <c r="G38" s="85"/>
       <c r="H38" s="82">
-        <v>115000</v>
+        <v>18500</v>
       </c>
       <c r="J38" s="87"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="85" t="s">
-        <v>184</v>
-      </c>
-      <c r="B39" s="162"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="169">
-        <v>18500</v>
-      </c>
-      <c r="J39" s="87"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="B39" s="161"/>
+      <c r="C39" s="154"/>
+      <c r="D39" s="154"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="154"/>
+      <c r="H39" s="82">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="85" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B40" s="161"/>
       <c r="C40" s="154"/>
@@ -4902,43 +4877,45 @@
       <c r="E40" s="154"/>
       <c r="F40" s="154"/>
       <c r="G40" s="154"/>
-      <c r="H40" s="169">
-        <v>58000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="85" t="s">
-        <v>170</v>
-      </c>
-      <c r="B41" s="161"/>
-      <c r="C41" s="154"/>
-      <c r="D41" s="154"/>
-      <c r="E41" s="154"/>
-      <c r="F41" s="154"/>
-      <c r="G41" s="154"/>
+      <c r="H40" s="82">
+        <v>235168.14</v>
+      </c>
+      <c r="I40" s="149"/>
+      <c r="J40" s="177"/>
+    </row>
+    <row r="41" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="235" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="236"/>
+      <c r="C41" s="236"/>
+      <c r="D41" s="236"/>
+      <c r="E41" s="236"/>
+      <c r="F41" s="236"/>
+      <c r="G41" s="237"/>
       <c r="H41" s="82">
-        <v>300000</v>
-      </c>
-      <c r="J41" s="185"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="85" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="161"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="154"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="154"/>
-      <c r="G42" s="154"/>
+        <v>450000</v>
+      </c>
+      <c r="J41" s="177"/>
+    </row>
+    <row r="42" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="190" t="s">
+        <v>173</v>
+      </c>
+      <c r="B42" s="191"/>
+      <c r="C42" s="191"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="191"/>
+      <c r="G42" s="192"/>
       <c r="H42" s="82">
-        <v>44800.12</v>
-      </c>
-      <c r="J42" s="185"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>741000</v>
+      </c>
+      <c r="J42" s="177"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="85" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B43" s="161"/>
       <c r="C43" s="154"/>
@@ -4947,321 +4924,307 @@
       <c r="F43" s="154"/>
       <c r="G43" s="154"/>
       <c r="H43" s="82">
-        <v>121997.24</v>
-      </c>
-      <c r="I43" s="149"/>
-      <c r="J43" s="185"/>
-    </row>
-    <row r="44" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="241" t="s">
-        <v>187</v>
-      </c>
-      <c r="B44" s="242"/>
-      <c r="C44" s="242"/>
-      <c r="D44" s="242"/>
-      <c r="E44" s="242"/>
-      <c r="F44" s="242"/>
-      <c r="G44" s="243"/>
-      <c r="H44" s="169">
+        <v>20000</v>
+      </c>
+      <c r="J43" s="177"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="161"/>
+      <c r="C44" s="154"/>
+      <c r="D44" s="154"/>
+      <c r="E44" s="154"/>
+      <c r="F44" s="154"/>
+      <c r="G44" s="154"/>
+      <c r="H44" s="82">
         <v>450000</v>
       </c>
-      <c r="J44" s="185"/>
-    </row>
-    <row r="45" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="182" t="s">
-        <v>188</v>
-      </c>
-      <c r="B45" s="183"/>
-      <c r="C45" s="183"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="183"/>
-      <c r="F45" s="183"/>
-      <c r="G45" s="184"/>
-      <c r="H45" s="169">
-        <v>741000</v>
-      </c>
-      <c r="J45" s="185"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="170" t="s">
-        <v>189</v>
-      </c>
-      <c r="B46" s="161"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="154"/>
-      <c r="E46" s="154"/>
-      <c r="F46" s="154"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="169">
-        <v>20000</v>
-      </c>
-      <c r="J46" s="185"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="85" t="s">
-        <v>186</v>
-      </c>
-      <c r="B47" s="161"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="154"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="154" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="154"/>
+      <c r="C45" s="154"/>
+      <c r="D45" s="154"/>
+      <c r="E45" s="154"/>
+      <c r="F45" s="154"/>
+      <c r="G45" s="154"/>
+      <c r="H45" s="84">
+        <f>SUM(H35:H44)</f>
+        <v>2150668.14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="218" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="218"/>
+      <c r="C46" s="218"/>
+      <c r="D46" s="218"/>
+      <c r="E46" s="218"/>
+      <c r="F46" s="218"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="218"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="154" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="154"/>
+      <c r="C47" s="154" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="163"/>
       <c r="E47" s="154"/>
       <c r="F47" s="154"/>
       <c r="G47" s="154"/>
-      <c r="H47" s="169">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="154" t="s">
-        <v>101</v>
+      <c r="H47" s="82">
+        <v>250000</v>
+      </c>
+      <c r="J47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="164" t="s">
+        <v>148</v>
       </c>
       <c r="B48" s="154"/>
-      <c r="C48" s="154"/>
-      <c r="D48" s="154"/>
-      <c r="E48" s="154"/>
-      <c r="F48" s="154"/>
+      <c r="C48" s="198"/>
+      <c r="D48" s="199"/>
+      <c r="E48" s="165"/>
+      <c r="F48" s="158"/>
       <c r="G48" s="154"/>
-      <c r="H48" s="84">
-        <f>SUM(H35:H47)</f>
-        <v>2497297.36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="224" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" s="224"/>
-      <c r="C49" s="224"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="224"/>
-      <c r="F49" s="224"/>
-      <c r="G49" s="224"/>
-      <c r="H49" s="224"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="154" t="s">
+      <c r="H48" s="82">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="154"/>
+      <c r="B49" s="154"/>
+      <c r="C49" s="158"/>
+      <c r="D49" s="158"/>
+      <c r="E49" s="158"/>
+      <c r="F49" s="158"/>
+      <c r="G49" s="154"/>
+      <c r="H49" s="82"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="157" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="157"/>
+      <c r="C50" s="157"/>
+      <c r="D50" s="157"/>
+      <c r="E50" s="157"/>
+      <c r="F50" s="157"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="84">
+        <f>SUM(H47:H49)</f>
+        <v>278000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="229" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="154"/>
-      <c r="C50" s="154" t="s">
-        <v>180</v>
-      </c>
-      <c r="D50" s="163"/>
-      <c r="E50" s="154"/>
-      <c r="F50" s="154"/>
-      <c r="G50" s="154"/>
-      <c r="H50" s="169">
-        <v>250000</v>
-      </c>
-      <c r="J50" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="164" t="s">
-        <v>149</v>
-      </c>
-      <c r="B51" s="154"/>
-      <c r="C51" s="220"/>
-      <c r="D51" s="221"/>
-      <c r="E51" s="165"/>
-      <c r="F51" s="158"/>
-      <c r="G51" s="154"/>
-      <c r="H51" s="169">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="154"/>
+      <c r="B51" s="230"/>
+      <c r="C51" s="230"/>
+      <c r="D51" s="230"/>
+      <c r="E51" s="230"/>
+      <c r="F51" s="230"/>
+      <c r="G51" s="230"/>
+      <c r="H51" s="231"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="154" t="s">
+        <v>117</v>
+      </c>
       <c r="B52" s="154"/>
-      <c r="C52" s="158"/>
-      <c r="D52" s="158"/>
-      <c r="E52" s="158"/>
-      <c r="F52" s="158"/>
+      <c r="C52" s="154"/>
+      <c r="D52" s="154"/>
+      <c r="E52" s="154"/>
+      <c r="F52" s="154"/>
       <c r="G52" s="154"/>
-      <c r="H52" s="82"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="157" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" s="157"/>
-      <c r="C53" s="157"/>
-      <c r="D53" s="157"/>
-      <c r="E53" s="157"/>
-      <c r="F53" s="157"/>
-      <c r="G53" s="157"/>
-      <c r="H53" s="84">
-        <f>SUM(H50:H52)</f>
-        <v>278000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="235" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="236"/>
-      <c r="C54" s="236"/>
-      <c r="D54" s="236"/>
-      <c r="E54" s="236"/>
-      <c r="F54" s="236"/>
-      <c r="G54" s="236"/>
-      <c r="H54" s="237"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="154" t="s">
+      <c r="H52" s="82">
+        <v>69571.37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="154"/>
+      <c r="B53" s="154"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="154"/>
+      <c r="E53" s="154"/>
+      <c r="F53" s="154"/>
+      <c r="G53" s="154"/>
+      <c r="H53" s="82"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="157" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="157"/>
+      <c r="C54" s="157"/>
+      <c r="D54" s="157"/>
+      <c r="E54" s="157"/>
+      <c r="F54" s="157"/>
+      <c r="G54" s="157"/>
+      <c r="H54" s="160">
+        <f>SUM(H52:H53)</f>
+        <v>69571.37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="229" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="154"/>
-      <c r="C55" s="154"/>
-      <c r="D55" s="154"/>
-      <c r="E55" s="154"/>
-      <c r="F55" s="154"/>
-      <c r="G55" s="154"/>
-      <c r="H55" s="82">
-        <v>61673.68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="154"/>
-      <c r="B56" s="154"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="154"/>
-      <c r="E56" s="154"/>
-      <c r="F56" s="154"/>
-      <c r="G56" s="154"/>
-      <c r="H56" s="82"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="157" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57" s="157"/>
-      <c r="C57" s="157"/>
-      <c r="D57" s="157"/>
-      <c r="E57" s="157"/>
-      <c r="F57" s="157"/>
-      <c r="G57" s="157"/>
-      <c r="H57" s="160">
-        <f>SUM(H55:H56)</f>
-        <v>61673.68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="235" t="s">
+      <c r="B55" s="230"/>
+      <c r="C55" s="230"/>
+      <c r="D55" s="230"/>
+      <c r="E55" s="230"/>
+      <c r="F55" s="230"/>
+      <c r="G55" s="230"/>
+      <c r="H55" s="231"/>
+      <c r="I55" s="87"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="85"/>
+      <c r="C56" s="85"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="85"/>
+      <c r="H56" s="82">
+        <v>49889.86</v>
+      </c>
+      <c r="I56" s="87"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="85" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" s="85"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="85"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="85"/>
+      <c r="H57" s="82">
+        <v>3498.02</v>
+      </c>
+      <c r="I57" s="87"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="85"/>
+      <c r="C58" s="85"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
+      <c r="H58" s="84">
+        <f>SUM(H56:H57)</f>
+        <v>53387.88</v>
+      </c>
+      <c r="I58" s="87"/>
+      <c r="K58" s="83"/>
+    </row>
+    <row r="59" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="232" t="s">
         <v>119</v>
       </c>
-      <c r="B58" s="236"/>
-      <c r="C58" s="236"/>
-      <c r="D58" s="236"/>
-      <c r="E58" s="236"/>
-      <c r="F58" s="236"/>
-      <c r="G58" s="236"/>
-      <c r="H58" s="237"/>
-      <c r="I58" s="87"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="B59" s="85"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="85"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
-      <c r="H59" s="82">
-        <v>49889.86</v>
-      </c>
-      <c r="I59" s="87"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="B60" s="85"/>
-      <c r="C60" s="85"/>
-      <c r="D60" s="85"/>
-      <c r="E60" s="85"/>
-      <c r="F60" s="85"/>
-      <c r="G60" s="85"/>
-      <c r="H60" s="82">
-        <v>3498.02</v>
-      </c>
-      <c r="I60" s="87"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="B61" s="85"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="85"/>
-      <c r="E61" s="85"/>
-      <c r="F61" s="85"/>
-      <c r="G61" s="85"/>
-      <c r="H61" s="84">
-        <f>SUM(H59:H60)</f>
-        <v>53387.88</v>
-      </c>
-      <c r="I61" s="87"/>
-      <c r="K61" s="83"/>
-    </row>
-    <row r="62" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="238" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="239"/>
-      <c r="C62" s="239"/>
-      <c r="D62" s="239"/>
-      <c r="E62" s="239"/>
-      <c r="F62" s="239"/>
-      <c r="G62" s="239"/>
-      <c r="H62" s="240"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="86"/>
-      <c r="B63" s="86"/>
-      <c r="C63" s="86"/>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
-      <c r="H63" s="90"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="86"/>
-      <c r="B64" s="86"/>
-      <c r="C64" s="86"/>
-      <c r="D64" s="86"/>
-      <c r="E64" s="86"/>
-      <c r="F64" s="86"/>
-      <c r="G64" s="86"/>
-      <c r="H64" s="90"/>
-    </row>
-    <row r="65" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A65" s="91" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" s="89"/>
-      <c r="C65" s="89"/>
-      <c r="D65" s="89"/>
-      <c r="E65" s="89"/>
-      <c r="F65" s="89"/>
-      <c r="G65" s="89"/>
-      <c r="H65" s="92"/>
-    </row>
-    <row r="66" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A66" s="93"/>
-      <c r="B66" s="132"/>
-      <c r="C66" s="132"/>
-      <c r="D66" s="132"/>
-      <c r="E66" s="132"/>
-      <c r="F66" s="132"/>
-      <c r="G66" s="132"/>
-      <c r="H66" s="94"/>
-    </row>
-    <row r="67" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="233"/>
+      <c r="C59" s="233"/>
+      <c r="D59" s="233"/>
+      <c r="E59" s="233"/>
+      <c r="F59" s="233"/>
+      <c r="G59" s="233"/>
+      <c r="H59" s="234"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="86"/>
+      <c r="B60" s="86"/>
+      <c r="C60" s="86"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
+      <c r="H60" s="90"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="86"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
+      <c r="H61" s="90"/>
+    </row>
+    <row r="62" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="89"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
+      <c r="H62" s="92"/>
+    </row>
+    <row r="63" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="93"/>
+      <c r="B63" s="132"/>
+      <c r="C63" s="132"/>
+      <c r="D63" s="132"/>
+      <c r="E63" s="132"/>
+      <c r="F63" s="132"/>
+      <c r="G63" s="132"/>
+      <c r="H63" s="94"/>
+    </row>
+    <row r="64" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="91"/>
+      <c r="B64" s="89"/>
+      <c r="C64" s="89"/>
+      <c r="D64" s="89"/>
+      <c r="E64" s="89"/>
+      <c r="F64" s="89"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="92"/>
+    </row>
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="200" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" s="201"/>
+      <c r="C65" s="201"/>
+      <c r="D65" s="201"/>
+      <c r="E65" s="201"/>
+      <c r="F65" s="201"/>
+      <c r="G65" s="201"/>
+      <c r="H65" s="128"/>
+    </row>
+    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="91"/>
+      <c r="B66" s="89"/>
+      <c r="C66" s="89"/>
+      <c r="D66" s="89"/>
+      <c r="E66" s="89"/>
+      <c r="F66" s="89"/>
+      <c r="G66" s="89"/>
+      <c r="H66" s="92"/>
+    </row>
+    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="91"/>
       <c r="B67" s="89"/>
       <c r="C67" s="89"/>
@@ -5271,19 +5234,22 @@
       <c r="G67" s="89"/>
       <c r="H67" s="92"/>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="222" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="223"/>
-      <c r="C68" s="223"/>
-      <c r="D68" s="223"/>
-      <c r="E68" s="223"/>
-      <c r="F68" s="223"/>
-      <c r="G68" s="223"/>
-      <c r="H68" s="128"/>
-    </row>
-    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="129" t="s">
+        <v>100</v>
+      </c>
+      <c r="B68" s="132"/>
+      <c r="C68" s="132"/>
+      <c r="D68" s="132"/>
+      <c r="E68" s="132"/>
+      <c r="F68" s="132"/>
+      <c r="G68" s="132"/>
+      <c r="H68" s="94">
+        <f>SUM(H66:H67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A69" s="91"/>
       <c r="B69" s="89"/>
       <c r="C69" s="89"/>
@@ -5293,342 +5259,351 @@
       <c r="G69" s="89"/>
       <c r="H69" s="92"/>
     </row>
-    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="91"/>
-      <c r="B70" s="89"/>
-      <c r="C70" s="89"/>
-      <c r="D70" s="89"/>
-      <c r="E70" s="89"/>
-      <c r="F70" s="89"/>
-      <c r="G70" s="89"/>
-      <c r="H70" s="92"/>
-    </row>
-    <row r="71" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="129" t="s">
-        <v>101</v>
-      </c>
-      <c r="B71" s="132"/>
-      <c r="C71" s="132"/>
-      <c r="D71" s="132"/>
-      <c r="E71" s="132"/>
-      <c r="F71" s="132"/>
-      <c r="G71" s="132"/>
-      <c r="H71" s="94">
-        <f>SUM(H69:H70)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A72" s="91"/>
-      <c r="B72" s="89"/>
-      <c r="C72" s="89"/>
-      <c r="D72" s="89"/>
-      <c r="E72" s="89"/>
-      <c r="F72" s="89"/>
-      <c r="G72" s="89"/>
-      <c r="H72" s="92"/>
-    </row>
-    <row r="73" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A73" s="216" t="s">
+    <row r="70" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A70" s="189" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="189"/>
+      <c r="C70" s="189"/>
+      <c r="D70" s="189"/>
+      <c r="E70" s="189"/>
+      <c r="F70" s="189"/>
+      <c r="G70" s="189"/>
+      <c r="H70" s="95"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="190"/>
+      <c r="B71" s="191"/>
+      <c r="C71" s="191"/>
+      <c r="D71" s="191"/>
+      <c r="E71" s="191"/>
+      <c r="F71" s="191"/>
+      <c r="G71" s="192"/>
+      <c r="H71" s="124"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="96"/>
+      <c r="B72" s="97"/>
+      <c r="C72" s="97"/>
+      <c r="D72" s="97"/>
+      <c r="E72" s="97"/>
+      <c r="F72" s="97"/>
+      <c r="G72" s="98"/>
+      <c r="H72" s="124"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="193"/>
+      <c r="B73" s="194"/>
+      <c r="C73" s="194"/>
+      <c r="D73" s="194"/>
+      <c r="E73" s="194"/>
+      <c r="F73" s="194"/>
+      <c r="G73" s="195"/>
+      <c r="H73" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="133"/>
+      <c r="B74" s="134"/>
+      <c r="C74" s="134"/>
+      <c r="D74" s="134"/>
+      <c r="E74" s="134"/>
+      <c r="F74" s="134"/>
+      <c r="G74" s="135"/>
+      <c r="H74" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="133"/>
+      <c r="B75" s="134"/>
+      <c r="C75" s="134"/>
+      <c r="D75" s="134"/>
+      <c r="E75" s="134"/>
+      <c r="F75" s="134"/>
+      <c r="G75" s="135"/>
+      <c r="H75" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="137" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="85"/>
+      <c r="C76" s="85"/>
+      <c r="D76" s="85"/>
+      <c r="E76" s="85"/>
+      <c r="F76" s="85"/>
+      <c r="G76" s="85"/>
+      <c r="H76" s="84">
+        <f>SUM(H71:H75)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="138"/>
+      <c r="B77" s="138"/>
+      <c r="C77" s="138"/>
+      <c r="D77" s="138"/>
+      <c r="E77" s="138"/>
+      <c r="F77" s="138"/>
+      <c r="G77" s="138"/>
+      <c r="H77" s="139"/>
+      <c r="I77" s="87"/>
+    </row>
+    <row r="78" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="216"/>
-      <c r="C73" s="216"/>
-      <c r="D73" s="216"/>
-      <c r="E73" s="216"/>
-      <c r="F73" s="216"/>
-      <c r="G73" s="216"/>
-      <c r="H73" s="95"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="182"/>
-      <c r="B74" s="183"/>
-      <c r="C74" s="183"/>
-      <c r="D74" s="183"/>
-      <c r="E74" s="183"/>
-      <c r="F74" s="183"/>
-      <c r="G74" s="184"/>
-      <c r="H74" s="124"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="96"/>
-      <c r="B75" s="97"/>
-      <c r="C75" s="97"/>
-      <c r="D75" s="97"/>
-      <c r="E75" s="97"/>
-      <c r="F75" s="97"/>
-      <c r="G75" s="98"/>
-      <c r="H75" s="124"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="217"/>
-      <c r="B76" s="218"/>
-      <c r="C76" s="218"/>
-      <c r="D76" s="218"/>
-      <c r="E76" s="218"/>
-      <c r="F76" s="218"/>
-      <c r="G76" s="219"/>
-      <c r="H76" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="133"/>
-      <c r="B77" s="134"/>
-      <c r="C77" s="134"/>
-      <c r="D77" s="134"/>
-      <c r="E77" s="134"/>
-      <c r="F77" s="134"/>
-      <c r="G77" s="135"/>
-      <c r="H77" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="133"/>
-      <c r="B78" s="134"/>
-      <c r="C78" s="134"/>
-      <c r="D78" s="134"/>
-      <c r="E78" s="134"/>
-      <c r="F78" s="134"/>
-      <c r="G78" s="135"/>
-      <c r="H78" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="137" t="s">
-        <v>101</v>
-      </c>
-      <c r="B79" s="85"/>
-      <c r="C79" s="85"/>
-      <c r="D79" s="85"/>
-      <c r="E79" s="85"/>
-      <c r="F79" s="85"/>
-      <c r="G79" s="85"/>
-      <c r="H79" s="84">
-        <f>SUM(H74:H78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="138"/>
-      <c r="B80" s="138"/>
-      <c r="C80" s="138"/>
-      <c r="D80" s="138"/>
-      <c r="E80" s="138"/>
-      <c r="F80" s="138"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="139"/>
+      <c r="B78" s="197"/>
+      <c r="C78" s="197"/>
+      <c r="D78" s="197"/>
+      <c r="E78" s="197"/>
+      <c r="F78" s="197"/>
+      <c r="G78" s="197"/>
+      <c r="H78" s="140">
+        <f>H76</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="87"/>
+    </row>
+    <row r="79" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="186" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="187"/>
+      <c r="C79" s="187"/>
+      <c r="D79" s="187"/>
+      <c r="E79" s="187"/>
+      <c r="F79" s="187"/>
+      <c r="G79" s="188"/>
+      <c r="H79" s="140"/>
+      <c r="I79" s="88"/>
+    </row>
+    <row r="80" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="202" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" s="203"/>
+      <c r="C80" s="203"/>
+      <c r="D80" s="203"/>
+      <c r="E80" s="203"/>
+      <c r="F80" s="203"/>
+      <c r="G80" s="204"/>
+      <c r="H80" s="140"/>
       <c r="I80" s="87"/>
-    </row>
-    <row r="81" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="198" t="s">
-        <v>122</v>
-      </c>
-      <c r="B81" s="199"/>
-      <c r="C81" s="199"/>
-      <c r="D81" s="199"/>
-      <c r="E81" s="199"/>
-      <c r="F81" s="199"/>
-      <c r="G81" s="199"/>
+      <c r="J80" s="83"/>
+    </row>
+    <row r="81" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A81" s="196" t="s">
+        <v>123</v>
+      </c>
+      <c r="B81" s="197"/>
+      <c r="C81" s="197"/>
+      <c r="D81" s="197"/>
+      <c r="E81" s="197"/>
+      <c r="F81" s="197"/>
+      <c r="G81" s="197"/>
       <c r="H81" s="140">
-        <f>H79</f>
-        <v>0</v>
-      </c>
-      <c r="I81" s="87"/>
-    </row>
-    <row r="82" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="213" t="s">
-        <v>123</v>
-      </c>
-      <c r="B82" s="214"/>
-      <c r="C82" s="214"/>
-      <c r="D82" s="214"/>
-      <c r="E82" s="214"/>
-      <c r="F82" s="214"/>
-      <c r="G82" s="215"/>
-      <c r="H82" s="140"/>
-      <c r="I82" s="88"/>
-    </row>
-    <row r="83" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="195" t="s">
-        <v>143</v>
-      </c>
-      <c r="B83" s="196"/>
-      <c r="C83" s="196"/>
-      <c r="D83" s="196"/>
-      <c r="E83" s="196"/>
-      <c r="F83" s="196"/>
-      <c r="G83" s="197"/>
-      <c r="H83" s="140"/>
-      <c r="I83" s="87"/>
-      <c r="J83" s="83"/>
-    </row>
-    <row r="84" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A84" s="198" t="s">
+        <f>H62+H58+H54+H50+H45+H33+H16+H21+H28+H68</f>
+        <v>5466659.8300000001</v>
+      </c>
+      <c r="I81" s="83"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A82" s="205" t="s">
         <v>124</v>
       </c>
-      <c r="B84" s="199"/>
-      <c r="C84" s="199"/>
-      <c r="D84" s="199"/>
-      <c r="E84" s="199"/>
-      <c r="F84" s="199"/>
-      <c r="G84" s="199"/>
-      <c r="H84" s="140">
-        <f>H65+H61+H57+H53+H48+H33+H16+H21+H28+H71</f>
-        <v>5172842.1300000008</v>
-      </c>
-      <c r="I84" s="83"/>
-    </row>
-    <row r="85" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A85" s="200" t="s">
+      <c r="B82" s="206"/>
+      <c r="C82" s="206"/>
+      <c r="D82" s="206"/>
+      <c r="E82" s="206"/>
+      <c r="F82" s="206"/>
+      <c r="G82" s="207"/>
+      <c r="H82" s="141">
+        <f>H81+H79</f>
+        <v>5466659.8300000001</v>
+      </c>
+      <c r="I82" s="83"/>
+      <c r="K82" s="149"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A83" s="205" t="s">
         <v>125</v>
       </c>
-      <c r="B85" s="201"/>
-      <c r="C85" s="201"/>
-      <c r="D85" s="201"/>
-      <c r="E85" s="201"/>
-      <c r="F85" s="201"/>
-      <c r="G85" s="202"/>
-      <c r="H85" s="141">
-        <f>H84+H82</f>
-        <v>5172842.1300000008</v>
-      </c>
-      <c r="I85" s="83"/>
-      <c r="K85" s="149"/>
-    </row>
-    <row r="86" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A86" s="200" t="s">
+      <c r="B83" s="206"/>
+      <c r="C83" s="206"/>
+      <c r="D83" s="206"/>
+      <c r="E83" s="206"/>
+      <c r="F83" s="206"/>
+      <c r="G83" s="207"/>
+      <c r="H83" s="142">
+        <f>H78+H80</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="83"/>
+    </row>
+    <row r="84" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="208" t="s">
         <v>126</v>
       </c>
-      <c r="B86" s="201"/>
-      <c r="C86" s="201"/>
-      <c r="D86" s="201"/>
-      <c r="E86" s="201"/>
-      <c r="F86" s="201"/>
-      <c r="G86" s="202"/>
-      <c r="H86" s="142">
-        <f>H81+H83</f>
-        <v>0</v>
-      </c>
-      <c r="I86" s="83"/>
-    </row>
-    <row r="87" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="203" t="s">
+      <c r="B84" s="209"/>
+      <c r="C84" s="209"/>
+      <c r="D84" s="209"/>
+      <c r="E84" s="209"/>
+      <c r="F84" s="209"/>
+      <c r="G84" s="209"/>
+      <c r="H84" s="143">
+        <f>H81+H78</f>
+        <v>5466659.8300000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="210" t="s">
         <v>127</v>
       </c>
-      <c r="B87" s="204"/>
-      <c r="C87" s="204"/>
-      <c r="D87" s="204"/>
-      <c r="E87" s="204"/>
-      <c r="F87" s="204"/>
-      <c r="G87" s="204"/>
-      <c r="H87" s="143">
-        <f>H84+H81</f>
-        <v>5172842.1300000008</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="205" t="s">
+      <c r="B85" s="211"/>
+      <c r="C85" s="211"/>
+      <c r="D85" s="211"/>
+      <c r="E85" s="211"/>
+      <c r="F85" s="211"/>
+      <c r="G85" s="211"/>
+      <c r="H85" s="100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="101"/>
+      <c r="B86" s="101"/>
+      <c r="C86" s="101"/>
+      <c r="D86" s="101"/>
+      <c r="E86" s="101"/>
+      <c r="F86" s="101"/>
+      <c r="G86" s="101"/>
+      <c r="H86" s="102"/>
+    </row>
+    <row r="87" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="212" t="s">
+        <v>162</v>
+      </c>
+      <c r="B87" s="213"/>
+      <c r="C87" s="213"/>
+      <c r="D87" s="213"/>
+      <c r="E87" s="213"/>
+      <c r="F87" s="213"/>
+      <c r="G87" s="213"/>
+      <c r="H87" s="214"/>
+    </row>
+    <row r="88" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="215"/>
+      <c r="B88" s="216"/>
+      <c r="C88" s="216"/>
+      <c r="D88" s="216"/>
+      <c r="E88" s="216"/>
+      <c r="F88" s="216"/>
+      <c r="G88" s="216"/>
+      <c r="H88" s="217"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+    </row>
+    <row r="90" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A90" s="178" t="s">
         <v>128</v>
       </c>
-      <c r="B88" s="206"/>
-      <c r="C88" s="206"/>
-      <c r="D88" s="206"/>
-      <c r="E88" s="206"/>
-      <c r="F88" s="206"/>
-      <c r="G88" s="206"/>
-      <c r="H88" s="100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="101"/>
-      <c r="B89" s="101"/>
-      <c r="C89" s="101"/>
-      <c r="D89" s="101"/>
-      <c r="E89" s="101"/>
-      <c r="F89" s="101"/>
-      <c r="G89" s="101"/>
-      <c r="H89" s="102"/>
-    </row>
-    <row r="90" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="207" t="s">
-        <v>165</v>
-      </c>
-      <c r="B90" s="208"/>
-      <c r="C90" s="208"/>
-      <c r="D90" s="208"/>
-      <c r="E90" s="208"/>
-      <c r="F90" s="208"/>
-      <c r="G90" s="208"/>
-      <c r="H90" s="209"/>
-    </row>
-    <row r="91" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="210"/>
-      <c r="B91" s="211"/>
-      <c r="C91" s="211"/>
-      <c r="D91" s="211"/>
-      <c r="E91" s="211"/>
-      <c r="F91" s="211"/>
-      <c r="G91" s="211"/>
-      <c r="H91" s="212"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-    </row>
-    <row r="93" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A93" s="186" t="s">
+      <c r="B90" s="179"/>
+      <c r="C90" s="179"/>
+      <c r="D90" s="179"/>
+      <c r="E90" s="179"/>
+      <c r="F90" s="179"/>
+      <c r="G90" s="179"/>
+      <c r="H90" s="180"/>
+    </row>
+    <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A91" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="B93" s="187"/>
-      <c r="C93" s="187"/>
-      <c r="D93" s="187"/>
-      <c r="E93" s="187"/>
-      <c r="F93" s="187"/>
-      <c r="G93" s="187"/>
-      <c r="H93" s="188"/>
-    </row>
-    <row r="94" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A94" s="103" t="s">
+      <c r="B91" s="104"/>
+      <c r="C91" s="104"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="104"/>
+      <c r="G91" s="104"/>
+      <c r="H91" s="105">
+        <v>1062593.9356154203</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B94" s="104"/>
-      <c r="C94" s="104"/>
-      <c r="D94" s="104"/>
-      <c r="E94" s="104"/>
-      <c r="F94" s="104"/>
-      <c r="G94" s="104"/>
-      <c r="H94" s="105">
-        <v>2065570.4002054194</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="s">
+      <c r="B92" s="106"/>
+      <c r="C92" s="106"/>
+      <c r="D92" s="106"/>
+      <c r="E92" s="106"/>
+      <c r="F92" s="106"/>
+      <c r="G92" s="106"/>
+      <c r="H92" s="18">
+        <f>Planilla!G43</f>
+        <v>5845602.4266750002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="107" t="s">
+        <v>136</v>
+      </c>
+      <c r="B93" s="108"/>
+      <c r="C93" s="108"/>
+      <c r="D93" s="108"/>
+      <c r="E93" s="108"/>
+      <c r="F93" s="108"/>
+      <c r="G93" s="108"/>
+      <c r="H93" s="123">
+        <f>-H84</f>
+        <v>-5466659.8300000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="107" t="s">
         <v>131</v>
       </c>
-      <c r="B95" s="106"/>
-      <c r="C95" s="106"/>
-      <c r="D95" s="106"/>
-      <c r="E95" s="106"/>
-      <c r="F95" s="106"/>
-      <c r="G95" s="106"/>
-      <c r="H95" s="18">
-        <f>Planilla!G43</f>
-        <v>4485513.2054100009</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B94" s="108"/>
+      <c r="C94" s="108"/>
+      <c r="D94" s="108"/>
+      <c r="E94" s="108"/>
+      <c r="F94" s="108"/>
+      <c r="G94" s="108"/>
+      <c r="H94" s="31">
+        <f>D110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="107" t="s">
+        <v>164</v>
+      </c>
+      <c r="B95" s="108"/>
+      <c r="C95" s="108"/>
+      <c r="D95" s="108"/>
+      <c r="E95" s="108"/>
+      <c r="F95" s="108"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="123">
+        <v>-155000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="107" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="B96" s="108"/>
       <c r="C96" s="108"/>
@@ -5637,276 +5612,188 @@
       <c r="F96" s="108"/>
       <c r="G96" s="108"/>
       <c r="H96" s="123">
-        <f>-H87</f>
-        <v>-5172842.1300000008</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-5745.4976506499997</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="B97" s="108"/>
+        <v>154</v>
+      </c>
+      <c r="B97" s="109"/>
       <c r="C97" s="108"/>
       <c r="D97" s="108"/>
       <c r="E97" s="108"/>
       <c r="F97" s="108"/>
       <c r="G97" s="108"/>
-      <c r="H97" s="31">
-        <f>D113</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="107" t="s">
-        <v>175</v>
-      </c>
-      <c r="B98" s="108"/>
-      <c r="C98" s="108"/>
-      <c r="D98" s="108"/>
-      <c r="E98" s="108"/>
-      <c r="F98" s="108"/>
-      <c r="G98" s="108"/>
-      <c r="H98" s="123">
-        <v>-225235</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="B99" s="108"/>
-      <c r="C99" s="108"/>
-      <c r="D99" s="108"/>
-      <c r="E99" s="108"/>
-      <c r="F99" s="108"/>
-      <c r="G99" s="108"/>
-      <c r="H99" s="123">
-        <v>-11102</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="107" t="s">
-        <v>156</v>
-      </c>
-      <c r="B100" s="109"/>
-      <c r="C100" s="108"/>
-      <c r="D100" s="108"/>
-      <c r="E100" s="108"/>
-      <c r="F100" s="108"/>
-      <c r="G100" s="108"/>
-      <c r="H100" s="131">
-        <f>-H71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A101" s="110" t="s">
+      <c r="H97" s="131">
+        <f>-H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A98" s="110" t="s">
+        <v>132</v>
+      </c>
+      <c r="B98" s="111"/>
+      <c r="C98" s="111"/>
+      <c r="D98" s="111"/>
+      <c r="E98" s="111"/>
+      <c r="F98" s="111"/>
+      <c r="G98" s="111"/>
+      <c r="H98" s="112">
+        <f>SUM(H91:H97)</f>
+        <v>1280791.0346397704</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="181" t="s">
         <v>133</v>
       </c>
-      <c r="B101" s="111"/>
-      <c r="C101" s="111"/>
-      <c r="D101" s="111"/>
-      <c r="E101" s="111"/>
-      <c r="F101" s="111"/>
-      <c r="G101" s="111"/>
-      <c r="H101" s="112">
-        <f>SUM(H94:H100)</f>
-        <v>1141904.4756154194</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="103" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="189" t="s">
-        <v>134</v>
-      </c>
-      <c r="B103" s="190"/>
-      <c r="C103" s="190"/>
-      <c r="D103" s="190"/>
-      <c r="E103" s="190"/>
-      <c r="F103" s="190"/>
-      <c r="G103" s="190"/>
-      <c r="H103" s="191"/>
-    </row>
-    <row r="104" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="B104" s="113"/>
-      <c r="C104" s="113"/>
-      <c r="D104" s="113"/>
-      <c r="E104" s="113"/>
-      <c r="F104" s="113"/>
-      <c r="G104" s="113"/>
-      <c r="H104" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="115"/>
-      <c r="C105" s="108"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="18"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="116"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="18"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="18"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="117" t="s">
-        <v>133</v>
-      </c>
-      <c r="B108" s="117"/>
-      <c r="C108" s="117"/>
-      <c r="D108" s="117"/>
-      <c r="E108" s="117"/>
-      <c r="F108" s="117"/>
-      <c r="G108" s="117"/>
-      <c r="H108" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="125" t="s">
-        <v>147</v>
+      <c r="B100" s="182"/>
+      <c r="C100" s="182"/>
+      <c r="D100" s="182"/>
+      <c r="E100" s="182"/>
+      <c r="F100" s="182"/>
+      <c r="G100" s="182"/>
+      <c r="H100" s="183"/>
+    </row>
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="113" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="113"/>
+      <c r="C101" s="113"/>
+      <c r="D101" s="113"/>
+      <c r="E101" s="113"/>
+      <c r="F101" s="113"/>
+      <c r="G101" s="113"/>
+      <c r="H101" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="6"/>
+      <c r="B102" s="115"/>
+      <c r="C102" s="108"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="18"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="6"/>
+      <c r="B103" s="116"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="18"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="18"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="B105" s="117"/>
+      <c r="C105" s="117"/>
+      <c r="D105" s="117"/>
+      <c r="E105" s="117"/>
+      <c r="F105" s="117"/>
+      <c r="G105" s="117"/>
+      <c r="H105" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="125" t="s">
+        <v>146</v>
+      </c>
+      <c r="B107" s="126"/>
+      <c r="C107" s="126"/>
+      <c r="D107" s="126"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="18"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="18"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="119" t="s">
+        <v>100</v>
       </c>
       <c r="B110" s="126"/>
       <c r="C110" s="126"/>
-      <c r="D110" s="126"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="18"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="18"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="119" t="s">
-        <v>101</v>
-      </c>
-      <c r="B113" s="126"/>
-      <c r="C113" s="126"/>
-      <c r="D113" s="136">
-        <f>SUM(D111:D112)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="125" t="s">
-        <v>148</v>
-      </c>
-      <c r="B115" s="119"/>
-      <c r="C115" s="119"/>
-      <c r="D115" s="119"/>
-    </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D110" s="136">
+        <f>SUM(D108:D109)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="125" t="s">
+        <v>147</v>
+      </c>
+      <c r="B112" s="119"/>
+      <c r="C112" s="119"/>
+      <c r="D112" s="119"/>
+    </row>
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="6"/>
+      <c r="B113" s="99"/>
+      <c r="C113" s="99"/>
+      <c r="D113" s="121"/>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="6"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="127"/>
+    </row>
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="127"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
-      <c r="B116" s="99"/>
-      <c r="C116" s="99"/>
-      <c r="D116" s="121"/>
-    </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="127"/>
-    </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="127"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="127"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="120" t="s">
-        <v>101</v>
-      </c>
-      <c r="B120" s="120"/>
-      <c r="C120" s="192">
-        <f>SUM(D116:D119)</f>
-        <v>0</v>
-      </c>
-      <c r="D120" s="193"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="194"/>
-      <c r="B123" s="194"/>
-      <c r="C123" s="194"/>
-      <c r="D123" s="194"/>
-      <c r="E123" s="194"/>
-      <c r="F123" s="194"/>
-      <c r="G123" s="194"/>
-      <c r="H123" s="194"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="194"/>
-      <c r="B124" s="194"/>
-      <c r="C124" s="194"/>
-      <c r="D124" s="194"/>
-      <c r="E124" s="194"/>
-      <c r="F124" s="194"/>
-      <c r="G124" s="194"/>
-      <c r="H124" s="194"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="194"/>
-      <c r="B125" s="194"/>
-      <c r="C125" s="194"/>
-      <c r="D125" s="194"/>
-      <c r="E125" s="194"/>
-      <c r="F125" s="194"/>
-      <c r="G125" s="194"/>
-      <c r="H125" s="194"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="194"/>
-      <c r="B126" s="194"/>
-      <c r="C126" s="194"/>
-      <c r="D126" s="194"/>
-      <c r="E126" s="194"/>
-      <c r="F126" s="194"/>
-      <c r="G126" s="194"/>
-      <c r="H126" s="194"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="127"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="120" t="s">
+        <v>100</v>
+      </c>
+      <c r="B117" s="120"/>
+      <c r="C117" s="184">
+        <f>SUM(D113:D116)</f>
+        <v>0</v>
+      </c>
+      <c r="D117" s="185"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A44:G44"/>
+  <mergeCells count="32">
+    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A87:H88"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -5914,26 +5801,29 @@
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A123:H126"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A82:G82"/>
     <mergeCell ref="A83:G83"/>
     <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A90:H91"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="J41:J46"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="A68:G68"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/YRIGOYEN 9115/Mayo/YRIGOYEN-EXPENSAS-MAYO.xlsx
+++ b/YRIGOYEN 9115/Mayo/YRIGOYEN-EXPENSAS-MAYO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9184C9A-439A-4117-9232-04C393FDA2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7ECB44-5C31-44A2-B07B-A372048C45AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
@@ -565,9 +565,6 @@
     <t>Sanitarios roma - compra caños de gas para perdida del dpto 9</t>
   </si>
   <si>
-    <t>Vaciamiento de guardia con bomba propia y del consorciopor ganado de agua de napa - Se asiste hasta su vaciamiento el dia 16/05 con personal - imputado a la uf PA</t>
-  </si>
-  <si>
     <t>Casa Koruk - compra de botas para la encargada</t>
   </si>
   <si>
@@ -578,6 +575,9 @@
   </si>
   <si>
     <t>Macarena perez ruiz</t>
+  </si>
+  <si>
+    <t>Vaciamiento de guardia con bomba propia y del consorcio por ganado de agua de napa - Se asiste hasta su vaciamiento el dia 16/05 con personal - imputado a la uf PA</t>
   </si>
 </sst>
 </file>
@@ -1705,6 +1705,99 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1745,15 +1838,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1803,90 +1887,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3971,7 +3971,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E37" s="30">
         <v>2.4899999999999999E-2</v>
@@ -4025,7 +4025,7 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E38" s="30">
         <v>2.1499999999999998E-2</v>
@@ -4368,23 +4368,23 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="219"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
+      <c r="D2" s="186"/>
+      <c r="E2" s="187"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="187"/>
+      <c r="H2" s="188"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="222" t="s">
+      <c r="E3" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="222"/>
-      <c r="G3" s="222"/>
-      <c r="H3" s="223"/>
+      <c r="F3" s="189"/>
+      <c r="G3" s="189"/>
+      <c r="H3" s="190"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
@@ -4452,16 +4452,16 @@
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="224" t="s">
+      <c r="A10" s="191" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="226"/>
+      <c r="B10" s="192"/>
+      <c r="C10" s="192"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="193"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
@@ -4474,16 +4474,16 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="227" t="s">
+      <c r="A12" s="194" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="227"/>
-      <c r="C12" s="227"/>
-      <c r="D12" s="227"/>
-      <c r="E12" s="227"/>
-      <c r="F12" s="227"/>
-      <c r="G12" s="227"/>
-      <c r="H12" s="227"/>
+      <c r="B12" s="194"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
+      <c r="F12" s="194"/>
+      <c r="G12" s="194"/>
+      <c r="H12" s="194"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="153" t="s">
@@ -4544,16 +4544,16 @@
       <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="228" t="s">
+      <c r="A17" s="195" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="228"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="228"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="228"/>
-      <c r="H17" s="228"/>
+      <c r="B17" s="195"/>
+      <c r="C17" s="195"/>
+      <c r="D17" s="195"/>
+      <c r="E17" s="195"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="195"/>
+      <c r="H17" s="195"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
@@ -4609,16 +4609,16 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="228" t="s">
+      <c r="A22" s="195" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="228"/>
-      <c r="C22" s="228"/>
-      <c r="D22" s="228"/>
-      <c r="E22" s="228"/>
-      <c r="F22" s="228"/>
-      <c r="G22" s="228"/>
-      <c r="H22" s="228"/>
+      <c r="B22" s="195"/>
+      <c r="C22" s="195"/>
+      <c r="D22" s="195"/>
+      <c r="E22" s="195"/>
+      <c r="F22" s="195"/>
+      <c r="G22" s="195"/>
+      <c r="H22" s="195"/>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="153" t="s">
@@ -4714,16 +4714,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="218" t="s">
+      <c r="A29" s="185" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="218"/>
-      <c r="C29" s="218"/>
-      <c r="D29" s="218"/>
-      <c r="E29" s="218"/>
-      <c r="F29" s="218"/>
-      <c r="G29" s="218"/>
-      <c r="H29" s="218"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="185"/>
+      <c r="D29" s="185"/>
+      <c r="E29" s="185"/>
+      <c r="F29" s="185"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="154" t="s">
@@ -4788,16 +4788,16 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
+      <c r="B34" s="185"/>
+      <c r="C34" s="185"/>
+      <c r="D34" s="185"/>
+      <c r="E34" s="185"/>
+      <c r="F34" s="185"/>
+      <c r="G34" s="185"/>
+      <c r="H34" s="185"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
@@ -4881,41 +4881,41 @@
         <v>235168.14</v>
       </c>
       <c r="I40" s="149"/>
-      <c r="J40" s="177"/>
+      <c r="J40" s="208"/>
     </row>
     <row r="41" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="235" t="s">
-        <v>178</v>
-      </c>
-      <c r="B41" s="236"/>
-      <c r="C41" s="236"/>
-      <c r="D41" s="236"/>
-      <c r="E41" s="236"/>
-      <c r="F41" s="236"/>
-      <c r="G41" s="237"/>
+      <c r="A41" s="202" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41" s="203"/>
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+      <c r="G41" s="204"/>
       <c r="H41" s="82">
         <v>450000</v>
       </c>
-      <c r="J41" s="177"/>
+      <c r="J41" s="208"/>
     </row>
     <row r="42" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="190" t="s">
+      <c r="A42" s="205" t="s">
         <v>173</v>
       </c>
-      <c r="B42" s="191"/>
-      <c r="C42" s="191"/>
-      <c r="D42" s="191"/>
-      <c r="E42" s="191"/>
-      <c r="F42" s="191"/>
-      <c r="G42" s="192"/>
+      <c r="B42" s="206"/>
+      <c r="C42" s="206"/>
+      <c r="D42" s="206"/>
+      <c r="E42" s="206"/>
+      <c r="F42" s="206"/>
+      <c r="G42" s="207"/>
       <c r="H42" s="82">
         <v>741000</v>
       </c>
-      <c r="J42" s="177"/>
+      <c r="J42" s="208"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B43" s="161"/>
       <c r="C43" s="154"/>
@@ -4926,7 +4926,7 @@
       <c r="H43" s="82">
         <v>20000</v>
       </c>
-      <c r="J43" s="177"/>
+      <c r="J43" s="208"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="85" t="s">
@@ -4958,16 +4958,16 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="218" t="s">
+      <c r="A46" s="185" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="218"/>
-      <c r="C46" s="218"/>
-      <c r="D46" s="218"/>
-      <c r="E46" s="218"/>
-      <c r="F46" s="218"/>
-      <c r="G46" s="218"/>
-      <c r="H46" s="218"/>
+      <c r="B46" s="185"/>
+      <c r="C46" s="185"/>
+      <c r="D46" s="185"/>
+      <c r="E46" s="185"/>
+      <c r="F46" s="185"/>
+      <c r="G46" s="185"/>
+      <c r="H46" s="185"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="154" t="s">
@@ -4993,8 +4993,8 @@
         <v>148</v>
       </c>
       <c r="B48" s="154"/>
-      <c r="C48" s="198"/>
-      <c r="D48" s="199"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="227"/>
       <c r="E48" s="165"/>
       <c r="F48" s="158"/>
       <c r="G48" s="154"/>
@@ -5028,16 +5028,16 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="229" t="s">
+      <c r="A51" s="196" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="230"/>
-      <c r="C51" s="230"/>
-      <c r="D51" s="230"/>
-      <c r="E51" s="230"/>
-      <c r="F51" s="230"/>
-      <c r="G51" s="230"/>
-      <c r="H51" s="231"/>
+      <c r="B51" s="197"/>
+      <c r="C51" s="197"/>
+      <c r="D51" s="197"/>
+      <c r="E51" s="197"/>
+      <c r="F51" s="197"/>
+      <c r="G51" s="197"/>
+      <c r="H51" s="198"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="154" t="s">
@@ -5079,16 +5079,16 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="229" t="s">
+      <c r="A55" s="196" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="230"/>
-      <c r="C55" s="230"/>
-      <c r="D55" s="230"/>
-      <c r="E55" s="230"/>
-      <c r="F55" s="230"/>
-      <c r="G55" s="230"/>
-      <c r="H55" s="231"/>
+      <c r="B55" s="197"/>
+      <c r="C55" s="197"/>
+      <c r="D55" s="197"/>
+      <c r="E55" s="197"/>
+      <c r="F55" s="197"/>
+      <c r="G55" s="197"/>
+      <c r="H55" s="198"/>
       <c r="I55" s="87"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -5139,16 +5139,16 @@
       <c r="K58" s="83"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="232" t="s">
+      <c r="A59" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="B59" s="233"/>
-      <c r="C59" s="233"/>
-      <c r="D59" s="233"/>
-      <c r="E59" s="233"/>
-      <c r="F59" s="233"/>
-      <c r="G59" s="233"/>
-      <c r="H59" s="234"/>
+      <c r="B59" s="200"/>
+      <c r="C59" s="200"/>
+      <c r="D59" s="200"/>
+      <c r="E59" s="200"/>
+      <c r="F59" s="200"/>
+      <c r="G59" s="200"/>
+      <c r="H59" s="201"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="86"/>
@@ -5203,15 +5203,15 @@
       <c r="H64" s="92"/>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="200" t="s">
+      <c r="A65" s="228" t="s">
         <v>153</v>
       </c>
-      <c r="B65" s="201"/>
-      <c r="C65" s="201"/>
-      <c r="D65" s="201"/>
-      <c r="E65" s="201"/>
-      <c r="F65" s="201"/>
-      <c r="G65" s="201"/>
+      <c r="B65" s="229"/>
+      <c r="C65" s="229"/>
+      <c r="D65" s="229"/>
+      <c r="E65" s="229"/>
+      <c r="F65" s="229"/>
+      <c r="G65" s="229"/>
       <c r="H65" s="128"/>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5260,25 +5260,25 @@
       <c r="H69" s="92"/>
     </row>
     <row r="70" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A70" s="189" t="s">
+      <c r="A70" s="220" t="s">
         <v>120</v>
       </c>
-      <c r="B70" s="189"/>
-      <c r="C70" s="189"/>
-      <c r="D70" s="189"/>
-      <c r="E70" s="189"/>
-      <c r="F70" s="189"/>
-      <c r="G70" s="189"/>
+      <c r="B70" s="220"/>
+      <c r="C70" s="220"/>
+      <c r="D70" s="220"/>
+      <c r="E70" s="220"/>
+      <c r="F70" s="220"/>
+      <c r="G70" s="220"/>
       <c r="H70" s="95"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="190"/>
-      <c r="B71" s="191"/>
-      <c r="C71" s="191"/>
-      <c r="D71" s="191"/>
-      <c r="E71" s="191"/>
-      <c r="F71" s="191"/>
-      <c r="G71" s="192"/>
+      <c r="A71" s="205"/>
+      <c r="B71" s="206"/>
+      <c r="C71" s="206"/>
+      <c r="D71" s="206"/>
+      <c r="E71" s="206"/>
+      <c r="F71" s="206"/>
+      <c r="G71" s="207"/>
       <c r="H71" s="124"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5292,13 +5292,13 @@
       <c r="H72" s="124"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="193"/>
-      <c r="B73" s="194"/>
-      <c r="C73" s="194"/>
-      <c r="D73" s="194"/>
-      <c r="E73" s="194"/>
-      <c r="F73" s="194"/>
-      <c r="G73" s="195"/>
+      <c r="A73" s="221"/>
+      <c r="B73" s="222"/>
+      <c r="C73" s="222"/>
+      <c r="D73" s="222"/>
+      <c r="E73" s="222"/>
+      <c r="F73" s="222"/>
+      <c r="G73" s="223"/>
       <c r="H73" s="82">
         <v>0</v>
       </c>
@@ -5354,15 +5354,15 @@
       <c r="I77" s="87"/>
     </row>
     <row r="78" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="196" t="s">
+      <c r="A78" s="224" t="s">
         <v>121</v>
       </c>
-      <c r="B78" s="197"/>
-      <c r="C78" s="197"/>
-      <c r="D78" s="197"/>
-      <c r="E78" s="197"/>
-      <c r="F78" s="197"/>
-      <c r="G78" s="197"/>
+      <c r="B78" s="225"/>
+      <c r="C78" s="225"/>
+      <c r="D78" s="225"/>
+      <c r="E78" s="225"/>
+      <c r="F78" s="225"/>
+      <c r="G78" s="225"/>
       <c r="H78" s="140">
         <f>H76</f>
         <v>0</v>
@@ -5370,42 +5370,42 @@
       <c r="I78" s="87"/>
     </row>
     <row r="79" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="186" t="s">
+      <c r="A79" s="217" t="s">
         <v>122</v>
       </c>
-      <c r="B79" s="187"/>
-      <c r="C79" s="187"/>
-      <c r="D79" s="187"/>
-      <c r="E79" s="187"/>
-      <c r="F79" s="187"/>
-      <c r="G79" s="188"/>
+      <c r="B79" s="218"/>
+      <c r="C79" s="218"/>
+      <c r="D79" s="218"/>
+      <c r="E79" s="218"/>
+      <c r="F79" s="218"/>
+      <c r="G79" s="219"/>
       <c r="H79" s="140"/>
       <c r="I79" s="88"/>
     </row>
     <row r="80" spans="1:10" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="202" t="s">
+      <c r="A80" s="230" t="s">
         <v>142</v>
       </c>
-      <c r="B80" s="203"/>
-      <c r="C80" s="203"/>
-      <c r="D80" s="203"/>
-      <c r="E80" s="203"/>
-      <c r="F80" s="203"/>
-      <c r="G80" s="204"/>
+      <c r="B80" s="231"/>
+      <c r="C80" s="231"/>
+      <c r="D80" s="231"/>
+      <c r="E80" s="231"/>
+      <c r="F80" s="231"/>
+      <c r="G80" s="232"/>
       <c r="H80" s="140"/>
       <c r="I80" s="87"/>
       <c r="J80" s="83"/>
     </row>
     <row r="81" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A81" s="196" t="s">
+      <c r="A81" s="224" t="s">
         <v>123</v>
       </c>
-      <c r="B81" s="197"/>
-      <c r="C81" s="197"/>
-      <c r="D81" s="197"/>
-      <c r="E81" s="197"/>
-      <c r="F81" s="197"/>
-      <c r="G81" s="197"/>
+      <c r="B81" s="225"/>
+      <c r="C81" s="225"/>
+      <c r="D81" s="225"/>
+      <c r="E81" s="225"/>
+      <c r="F81" s="225"/>
+      <c r="G81" s="225"/>
       <c r="H81" s="140">
         <f>H62+H58+H54+H50+H45+H33+H16+H21+H28+H68</f>
         <v>5466659.8300000001</v>
@@ -5413,15 +5413,15 @@
       <c r="I81" s="83"/>
     </row>
     <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A82" s="205" t="s">
+      <c r="A82" s="233" t="s">
         <v>124</v>
       </c>
-      <c r="B82" s="206"/>
-      <c r="C82" s="206"/>
-      <c r="D82" s="206"/>
-      <c r="E82" s="206"/>
-      <c r="F82" s="206"/>
-      <c r="G82" s="207"/>
+      <c r="B82" s="234"/>
+      <c r="C82" s="234"/>
+      <c r="D82" s="234"/>
+      <c r="E82" s="234"/>
+      <c r="F82" s="234"/>
+      <c r="G82" s="235"/>
       <c r="H82" s="141">
         <f>H81+H79</f>
         <v>5466659.8300000001</v>
@@ -5430,15 +5430,15 @@
       <c r="K82" s="149"/>
     </row>
     <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A83" s="205" t="s">
+      <c r="A83" s="233" t="s">
         <v>125</v>
       </c>
-      <c r="B83" s="206"/>
-      <c r="C83" s="206"/>
-      <c r="D83" s="206"/>
-      <c r="E83" s="206"/>
-      <c r="F83" s="206"/>
-      <c r="G83" s="207"/>
+      <c r="B83" s="234"/>
+      <c r="C83" s="234"/>
+      <c r="D83" s="234"/>
+      <c r="E83" s="234"/>
+      <c r="F83" s="234"/>
+      <c r="G83" s="235"/>
       <c r="H83" s="142">
         <f>H78+H80</f>
         <v>0</v>
@@ -5446,30 +5446,30 @@
       <c r="I83" s="83"/>
     </row>
     <row r="84" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="208" t="s">
+      <c r="A84" s="236" t="s">
         <v>126</v>
       </c>
-      <c r="B84" s="209"/>
-      <c r="C84" s="209"/>
-      <c r="D84" s="209"/>
-      <c r="E84" s="209"/>
-      <c r="F84" s="209"/>
-      <c r="G84" s="209"/>
+      <c r="B84" s="237"/>
+      <c r="C84" s="237"/>
+      <c r="D84" s="237"/>
+      <c r="E84" s="237"/>
+      <c r="F84" s="237"/>
+      <c r="G84" s="237"/>
       <c r="H84" s="143">
         <f>H81+H78</f>
         <v>5466659.8300000001</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="210" t="s">
+      <c r="A85" s="177" t="s">
         <v>127</v>
       </c>
-      <c r="B85" s="211"/>
-      <c r="C85" s="211"/>
-      <c r="D85" s="211"/>
-      <c r="E85" s="211"/>
-      <c r="F85" s="211"/>
-      <c r="G85" s="211"/>
+      <c r="B85" s="178"/>
+      <c r="C85" s="178"/>
+      <c r="D85" s="178"/>
+      <c r="E85" s="178"/>
+      <c r="F85" s="178"/>
+      <c r="G85" s="178"/>
       <c r="H85" s="100">
         <v>0</v>
       </c>
@@ -5485,26 +5485,26 @@
       <c r="H86" s="102"/>
     </row>
     <row r="87" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="212" t="s">
+      <c r="A87" s="179" t="s">
         <v>162</v>
       </c>
-      <c r="B87" s="213"/>
-      <c r="C87" s="213"/>
-      <c r="D87" s="213"/>
-      <c r="E87" s="213"/>
-      <c r="F87" s="213"/>
-      <c r="G87" s="213"/>
-      <c r="H87" s="214"/>
+      <c r="B87" s="180"/>
+      <c r="C87" s="180"/>
+      <c r="D87" s="180"/>
+      <c r="E87" s="180"/>
+      <c r="F87" s="180"/>
+      <c r="G87" s="180"/>
+      <c r="H87" s="181"/>
     </row>
     <row r="88" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="215"/>
-      <c r="B88" s="216"/>
-      <c r="C88" s="216"/>
-      <c r="D88" s="216"/>
-      <c r="E88" s="216"/>
-      <c r="F88" s="216"/>
-      <c r="G88" s="216"/>
-      <c r="H88" s="217"/>
+      <c r="A88" s="182"/>
+      <c r="B88" s="183"/>
+      <c r="C88" s="183"/>
+      <c r="D88" s="183"/>
+      <c r="E88" s="183"/>
+      <c r="F88" s="183"/>
+      <c r="G88" s="183"/>
+      <c r="H88" s="184"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
@@ -5517,16 +5517,16 @@
       <c r="H89" s="6"/>
     </row>
     <row r="90" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A90" s="178" t="s">
+      <c r="A90" s="209" t="s">
         <v>128</v>
       </c>
-      <c r="B90" s="179"/>
-      <c r="C90" s="179"/>
-      <c r="D90" s="179"/>
-      <c r="E90" s="179"/>
-      <c r="F90" s="179"/>
-      <c r="G90" s="179"/>
-      <c r="H90" s="180"/>
+      <c r="B90" s="210"/>
+      <c r="C90" s="210"/>
+      <c r="D90" s="210"/>
+      <c r="E90" s="210"/>
+      <c r="F90" s="210"/>
+      <c r="G90" s="210"/>
+      <c r="H90" s="211"/>
     </row>
     <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A91" s="103" t="s">
@@ -5603,7 +5603,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="107" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B96" s="108"/>
       <c r="C96" s="108"/>
@@ -5647,16 +5647,16 @@
     </row>
     <row r="99" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="100" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="181" t="s">
+      <c r="A100" s="212" t="s">
         <v>133</v>
       </c>
-      <c r="B100" s="182"/>
-      <c r="C100" s="182"/>
-      <c r="D100" s="182"/>
-      <c r="E100" s="182"/>
-      <c r="F100" s="182"/>
-      <c r="G100" s="182"/>
-      <c r="H100" s="183"/>
+      <c r="B100" s="213"/>
+      <c r="C100" s="213"/>
+      <c r="D100" s="213"/>
+      <c r="E100" s="213"/>
+      <c r="F100" s="213"/>
+      <c r="G100" s="213"/>
+      <c r="H100" s="214"/>
     </row>
     <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="113" t="s">
@@ -5784,14 +5784,30 @@
         <v>100</v>
       </c>
       <c r="B117" s="120"/>
-      <c r="C117" s="184">
+      <c r="C117" s="215">
         <f>SUM(D113:D116)</f>
         <v>0</v>
       </c>
-      <c r="D117" s="185"/>
+      <c r="D117" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="A87:H88"/>
     <mergeCell ref="A29:H29"/>
@@ -5808,22 +5824,6 @@
     <mergeCell ref="A59:H59"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A42:G42"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A100:H100"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A84:G84"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
